--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Leafy Sour Watermelon Gummies 5mg THC 10 Pack</t>
+          <t>Leafy Maui Pineapple Gummies 5mg THC 10 Pack</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1096</v>
+        <v>1010</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="E2" t="n">
-        <v>136.1</v>
+        <v>136.7</v>
       </c>
       <c r="F2" t="n">
         <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="I2" t="n">
         <v>3.12</v>
       </c>
       <c r="J2" t="n">
-        <v>406</v>
+        <v>717</v>
       </c>
       <c r="K2" t="n">
         <v>36.9</v>
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Leafy Maui Pineapple Gummies 5mg THC 10 Pack</t>
+          <t>Leafy Sour Watermelon Gummies 5mg THC 10 Pack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,28 +540,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1017</v>
+        <v>1069</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="E3" t="n">
-        <v>134.7</v>
+        <v>135.9</v>
       </c>
       <c r="F3" t="n">
         <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="I3" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="J3" t="n">
-        <v>623</v>
+        <v>499</v>
       </c>
       <c r="K3" t="n">
         <v>36.9</v>
@@ -584,28 +584,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>424</v>
+        <v>513</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>65.3</v>
+        <v>62.9</v>
       </c>
       <c r="F4" t="n">
         <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="I4" t="n">
-        <v>26.46</v>
+        <v>26.44</v>
       </c>
       <c r="J4" t="n">
-        <v>4340</v>
+        <v>1428</v>
       </c>
       <c r="K4" t="n">
         <v>35.5</v>
@@ -627,28 +627,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>106.5</v>
+        <v>107.2</v>
       </c>
       <c r="F5" t="n">
         <v>1.19</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I5" t="n">
         <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>1920</v>
+        <v>1728</v>
       </c>
       <c r="K5" t="n">
         <v>33.1</v>
@@ -674,28 +674,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>285</v>
+        <v>228</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="E6" t="n">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>1.19</v>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>1728</v>
+        <v>2304</v>
       </c>
       <c r="K6" t="n">
         <v>33.1</v>
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uncle Arnie's Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Bent Paddle Puff Puff Pass Variety 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -721,41 +721,38 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>314</v>
+        <v>174</v>
       </c>
       <c r="D7" t="n">
-        <v>8.9</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>35.1</v>
+        <v>43.6</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="I7" t="n">
-        <v>26.4</v>
+        <v>22.5</v>
       </c>
       <c r="J7" t="n">
-        <v>106</v>
+        <v>1485</v>
       </c>
       <c r="K7" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>20</v>
+        <v>37.4</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bent Paddle Puff Puff Pass Variety 10mg THC 12pk 12oz can</t>
+          <t>Insight Flavor Pixels Black Lemon 10mg 12pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,38 +761,42 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="D8" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="E8" t="n">
-        <v>43.2</v>
+        <v>19.5</v>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I8" t="n">
-        <v>22.5</v>
+        <v>24.78</v>
       </c>
       <c r="J8" t="n">
-        <v>1620</v>
+        <v>1685</v>
       </c>
       <c r="K8" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Insight Flavor Pixels Black Lemon 10mg 12pk 12oz can</t>
+          <t>Happy Duck Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -804,85 +805,92 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="D9" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>19.4</v>
+        <v>40.7</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H9" t="n">
-        <v>66</v>
+        <v>174</v>
       </c>
       <c r="I9" t="n">
-        <v>24.78</v>
+        <v>5.86</v>
       </c>
       <c r="J9" t="n">
-        <v>1635</v>
+        <v>1019</v>
       </c>
       <c r="K9" t="n">
-        <v>34.7</v>
+        <v>51.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>37.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Quarterly buy</t>
+          <t>15c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Uncle Arnie's Strawberry Kiwi 10mg THC 2oz</t>
+          <t>Minny Grown Highbernate 5mg THC 10 Pack</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Edibles</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1414</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="E10" t="n">
-        <v>327.2</v>
+        <v>61.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>1.67</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K10" t="n">
-        <v>43.7</v>
+        <v>33.1</v>
       </c>
       <c r="L10" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Looner Wild Grape 10mg THC 4pk 12oz can</t>
+          <t>Uncle Arnie's Strawberry Kiwi 10mg THC 2oz</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -891,35 +899,41 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>309.65</v>
+        <v>1416</v>
       </c>
       <c r="D11" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="E11" t="n">
-        <v>67.3</v>
+        <v>324.8</v>
       </c>
       <c r="F11" t="n">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>11.2</v>
+        <v>1.67</v>
       </c>
       <c r="J11" t="n">
-        <v>202</v>
+        <v>80</v>
+      </c>
+      <c r="K11" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>23.1</v>
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Looner Root Beer 10mg THC Soda 4pk 12oz can</t>
+          <t>Looner Wild Grape 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -928,35 +942,35 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>282.25</v>
+        <v>280.65</v>
       </c>
       <c r="D12" t="n">
         <v>4.3</v>
       </c>
       <c r="E12" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="F12" t="n">
         <v>0.96</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I12" t="n">
         <v>11.2</v>
       </c>
       <c r="J12" t="n">
-        <v>403</v>
+        <v>470</v>
       </c>
       <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uncle Arnie's Tahitian Treat 10mg THC 2oz</t>
+          <t>Looner Root Beer 10mg THC Soda 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -965,72 +979,82 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>826</v>
+        <v>261</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>260.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F13" t="n">
         <v>0.96</v>
       </c>
       <c r="G13" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>432</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
-        <v>1.67</v>
+        <v>11.2</v>
       </c>
       <c r="J13" t="n">
-        <v>720</v>
+        <v>672</v>
       </c>
       <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Looner Professor Pepper 10mg THC 4pk 12oz can</t>
+          <t>Minny Grown BlueBeary 10 Pack</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Edibles</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>271.75</v>
+        <v>262</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="E14" t="n">
-        <v>57.2</v>
+        <v>49.8</v>
       </c>
       <c r="F14" t="n">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I14" t="n">
-        <v>11.2</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>67</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
+        <v>288</v>
+      </c>
+      <c r="K14" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Happy Duck Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Happy Duck Bomba 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1039,28 +1063,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>28.3</v>
+        <v>41.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="G15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I15" t="n">
-        <v>5.95</v>
+        <v>5.94</v>
       </c>
       <c r="J15" t="n">
-        <v>321</v>
+        <v>356</v>
       </c>
       <c r="K15" t="n">
         <v>51.2</v>
@@ -1077,54 +1101,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Minny Grown St. Croix Sunrise Yummy Gummy Bar 50mg THC</t>
+          <t>Uncle Arnie's Tahitian Treat 10mg THC 2oz</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Edibles</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>132</v>
+        <v>902</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E16" t="n">
-        <v>33.1</v>
+        <v>255.8</v>
       </c>
       <c r="F16" t="n">
-        <v>1.69</v>
+        <v>0.96</v>
       </c>
       <c r="G16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>156</v>
+        <v>336</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>1.67</v>
       </c>
       <c r="J16" t="n">
-        <v>936</v>
-      </c>
-      <c r="K16" t="n">
-        <v>33</v>
-      </c>
-      <c r="L16" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Insight Flavor Pixels 10mg THC Variety #2 12pk 12oz can</t>
+          <t>Looner Sweet Orange 10mg THC Soda 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1133,146 +1147,156 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>93</v>
+        <v>219.25</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="E17" t="n">
-        <v>19.9</v>
+        <v>48.6</v>
       </c>
       <c r="F17" t="n">
         <v>0.96</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>24.78</v>
+        <v>11.2</v>
       </c>
       <c r="J17" t="n">
-        <v>99</v>
-      </c>
-      <c r="K17" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Minny Grown Highbernate Moon Melon 5mg THC 10mg CBD 20mg CBN 10pk</t>
+          <t>Insight Flavor Pixels 10mg THC Variety #2 12pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Edibles</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="E18" t="n">
-        <v>30.8</v>
+        <v>19.1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>5.42</v>
+        <v>24.78</v>
       </c>
       <c r="J18" t="n">
-        <v>195</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K18" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Looner Sweet Orange 10mg THC Soda 4pk 12oz can</t>
+          <t>Minny Grown St. Croix Sunrise Yummy Gummy Bar 50mg THC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Edibles</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>206.25</v>
+        <v>123</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="E19" t="n">
-        <v>48.7</v>
+        <v>31.2</v>
       </c>
       <c r="F19" t="n">
-        <v>0.96</v>
+        <v>1.69</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>144</v>
       </c>
       <c r="I19" t="n">
-        <v>11.2</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>336</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
+        <v>864</v>
+      </c>
+      <c r="K19" t="n">
+        <v>33</v>
+      </c>
+      <c r="L19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uncle Arnie's Lemon Mint 10mg THC 2oz</t>
+          <t>Minny Grown Highbernate Moon Melon 5mg THC 10mg CBD 20mg CBN 10pk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Edibles</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>818</v>
+        <v>96</v>
       </c>
       <c r="D20" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="E20" t="n">
-        <v>186.5</v>
+        <v>27.8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="I20" t="n">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="J20" t="n">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="M20" t="inlineStr"/>
     </row>
@@ -1288,28 +1312,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D21" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="E21" t="n">
-        <v>39.2</v>
+        <v>42.5</v>
       </c>
       <c r="F21" t="n">
         <v>0.96</v>
       </c>
       <c r="G21" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I21" t="n">
         <v>14</v>
       </c>
       <c r="J21" t="n">
-        <v>364</v>
+        <v>560</v>
       </c>
       <c r="K21" t="n">
         <v>33.2</v>
@@ -1335,28 +1359,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="D22" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="E22" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="F22" t="n">
         <v>1.21</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I22" t="n">
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="K22" t="n">
         <v>37.3</v>
@@ -1378,28 +1402,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D23" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="E23" t="n">
-        <v>28.8</v>
+        <v>28.5</v>
       </c>
       <c r="F23" t="n">
         <v>1.1</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I23" t="n">
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="K23" t="n">
         <v>37.3</v>
@@ -1416,7 +1440,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Insight Brewing Flavor Pixels 12pk 12oz can</t>
+          <t>Climbing Kites Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1425,42 +1449,45 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="D24" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="E24" t="n">
-        <v>11.8</v>
+        <v>22.8</v>
       </c>
       <c r="F24" t="n">
-        <v>1.31</v>
+        <v>0.96</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>17.41</v>
+        <v>14.4</v>
       </c>
       <c r="J24" t="n">
-        <v>209</v>
+        <v>58</v>
       </c>
       <c r="K24" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Quarterly buy</t>
+          <t>Case 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Uncle Arnie's Cherry Limeade 10mg THC 4pk 12oz can</t>
+          <t>Jixxie 10mg Variety Pack 12pk 12oz cans</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1469,41 +1496,35 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="D25" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="E25" t="n">
-        <v>35.4</v>
+        <v>14.9</v>
       </c>
       <c r="F25" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I25" t="n">
-        <v>10.04</v>
+        <v>20.43</v>
       </c>
       <c r="J25" t="n">
-        <v>181</v>
-      </c>
-      <c r="K25" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>21.1</v>
+        <v>163</v>
       </c>
       <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jixxie 10mg Variety Pack 12pk 12oz cans</t>
+          <t>Insight Brewing Flavor Pixels 12pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1512,35 +1533,42 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D26" t="n">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="E26" t="n">
-        <v>13.7</v>
+        <v>10.9</v>
       </c>
       <c r="F26" t="n">
-        <v>0.96</v>
+        <v>1.31</v>
       </c>
       <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
         <v>4</v>
       </c>
-      <c r="H26" t="n">
-        <v>8</v>
-      </c>
       <c r="I26" t="n">
-        <v>20.64</v>
+        <v>17.41</v>
       </c>
       <c r="J26" t="n">
-        <v>165</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="K26" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Uncle Arnie's Straw Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Looner Diet Professor Pepper 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1549,41 +1577,35 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="D27" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="E27" t="n">
-        <v>28.6</v>
+        <v>24.3</v>
       </c>
       <c r="F27" t="n">
-        <v>1.15</v>
+        <v>0.96</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="J27" t="n">
-        <v>60</v>
-      </c>
-      <c r="K27" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>21.1</v>
+        <v>336</v>
       </c>
       <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>North Canna High Tonics Variety Pack 10mg THC</t>
+          <t>Looner Diet Root Beer 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1592,38 +1614,35 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="D28" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="F28" t="n">
         <v>0.96</v>
       </c>
       <c r="G28" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="I28" t="n">
-        <v>16.67</v>
+        <v>11.2</v>
       </c>
       <c r="J28" t="n">
-        <v>800</v>
-      </c>
-      <c r="K28" t="n">
-        <v>35.8</v>
+        <v>269</v>
       </c>
       <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Looner Diet Professor Pepper 10mg 4pk 12oz can</t>
+          <t>You Betcha Jasmine Green Tea 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1632,16 +1651,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D29" t="n">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="E29" t="n">
-        <v>18.8</v>
+        <v>13.9</v>
       </c>
       <c r="F29" t="n">
-        <v>0.96</v>
+        <v>1.49</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -1650,57 +1669,74 @@
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>67</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="K29" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yellow (Daytime)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bent Paddle Puff Party Pack 10mg THC 12pk 12oz can</t>
+          <t>Minny Grown Caramel Apple Alien Abduction Yummy Gummy Bar 50mg THC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Edibles</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D30" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="E30" t="n">
-        <v>9.9</v>
+        <v>17</v>
       </c>
       <c r="F30" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I30" t="n">
-        <v>22.71</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="K30" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="L30" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Collective Project Orange Vanilla 10mg THC 4pk 12oz can</t>
+          <t>THC Mystery Box 12pk</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1709,41 +1745,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>6.7</v>
+        <v>0.1</v>
       </c>
       <c r="E31" t="n">
-        <v>14.6</v>
+        <v>34.2</v>
       </c>
       <c r="F31" t="n">
-        <v>1.46</v>
+        <v>0.96</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="H31" t="n">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="I31" t="n">
-        <v>9.33</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>112</v>
-      </c>
-      <c r="K31" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="L31" t="n">
-        <v>30</v>
+        <v>1304</v>
       </c>
       <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Minny Grown Highbernate Sleepy Time Tonic 10mg THC</t>
+          <t>North Canna High Tonics Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1752,45 +1782,38 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="E32" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="F32" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="I32" t="n">
-        <v>11</v>
+        <v>16.67</v>
       </c>
       <c r="J32" t="n">
-        <v>66</v>
+        <v>700</v>
       </c>
       <c r="K32" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+        <v>35.8</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Voltage Lavender Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Collective Project Orange Vanilla 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1799,75 +1822,81 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D33" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="E33" t="n">
-        <v>12.8</v>
+        <v>14.9</v>
       </c>
       <c r="F33" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I33" t="n">
-        <v>7.28</v>
+        <v>9.33</v>
       </c>
       <c r="J33" t="n">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="K33" t="n">
-        <v>30.6</v>
+        <v>41.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>30</v>
       </c>
       <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>THC Mystery Box 12pk</t>
+          <t>Granny's Rainbow Sherbet 5mg THC Gummies 10pk</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Edibles</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="E34" t="n">
-        <v>24.5</v>
+        <v>36.6</v>
       </c>
       <c r="F34" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="G34" t="n">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>5.79</v>
       </c>
       <c r="J34" t="n">
-        <v>936</v>
+        <v>116</v>
+      </c>
+      <c r="K34" t="n">
+        <v>36.4</v>
       </c>
       <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wild State Birdie Grapefruit Twist 10mg THC 4pk 12oz can</t>
+          <t>Minny Grown Highbernate Sleepy Time Tonic 10mg THC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1876,68 +1905,78 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="E35" t="n">
-        <v>9.300000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="F35" t="n">
-        <v>1.09</v>
+        <v>0.77</v>
       </c>
       <c r="G35" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I35" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="J35" t="n">
-        <v>264</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
+        <v>132</v>
+      </c>
+      <c r="K35" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Granny's Rainbow Sherbet 5mg THC Gummies 10pk</t>
+          <t>Voltage Lavender Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Edibles</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="E36" t="n">
-        <v>34.2</v>
+        <v>11.7</v>
       </c>
       <c r="F36" t="n">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>5.83</v>
+        <v>7.27</v>
       </c>
       <c r="J36" t="n">
-        <v>233</v>
+        <v>44</v>
       </c>
       <c r="K36" t="n">
-        <v>36.4</v>
+        <v>30.6</v>
       </c>
       <c r="M36" t="inlineStr"/>
     </row>
@@ -1953,13 +1992,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D37" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="E37" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="F37" t="n">
         <v>1.51</v>
@@ -1981,7 +2020,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Modist Melt Hot Box THC 10mg Variety 12pk 12oz can</t>
+          <t>High Rise Pineapple 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1990,45 +2029,35 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="D38" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="E38" t="n">
-        <v>4.5</v>
+        <v>12.6</v>
       </c>
       <c r="F38" t="n">
         <v>0.96</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J38" t="n">
-        <v>220</v>
-      </c>
-      <c r="K38" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="L38" t="n">
-        <v>20</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>North Canna High Tonics Blood Orange Mango 10mg THC</t>
+          <t>Wild State Birdie Grapefruit Twist 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2037,38 +2066,35 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="E39" t="n">
-        <v>13.6</v>
+        <v>7.3</v>
       </c>
       <c r="F39" t="n">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="G39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H39" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I39" t="n">
-        <v>9.67</v>
+        <v>5.5</v>
       </c>
       <c r="J39" t="n">
-        <v>522</v>
-      </c>
-      <c r="K39" t="n">
-        <v>35.4</v>
+        <v>231</v>
       </c>
       <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>North Canna High Tonics Strawberry Melon 10mg THC</t>
+          <t>Modist Melt Hot Box THC 10mg Variety 12pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2077,38 +2103,45 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D40" t="n">
         <v>2.9</v>
       </c>
       <c r="E40" t="n">
-        <v>13.4</v>
+        <v>3.9</v>
       </c>
       <c r="F40" t="n">
         <v>0.96</v>
       </c>
       <c r="G40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I40" t="n">
-        <v>9.67</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>290</v>
+        <v>176</v>
       </c>
       <c r="K40" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
+        <v>35.2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>20</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine 100cs Buy</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Modist Melt Ginger Lemon Lime THC 10mg 4pk 12oz can</t>
+          <t>North Canna High Tonics Strawberry Melon 10mg THC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2117,45 +2150,38 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D41" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>10.6</v>
+        <v>12</v>
       </c>
       <c r="F41" t="n">
         <v>0.96</v>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H41" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I41" t="n">
-        <v>9.220000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="J41" t="n">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="K41" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="L41" t="n">
-        <v>20</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+        <v>35.4</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>North Canna High Tonics Prickly Pear Lime 10mg THC</t>
+          <t>North Canna High Tonics Blood Orange Mango 10mg THC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2164,28 +2190,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D42" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="E42" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="F42" t="n">
         <v>0.96</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I42" t="n">
-        <v>9.69</v>
+        <v>9.67</v>
       </c>
       <c r="J42" t="n">
-        <v>232</v>
+        <v>464</v>
       </c>
       <c r="K42" t="n">
         <v>35.4</v>
@@ -2195,7 +2221,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>North Canna High Tonics Prickly Pear Lime 10mg THC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2204,41 +2230,38 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D43" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="F43" t="n">
-        <v>1.24</v>
+        <v>0.96</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I43" t="n">
-        <v>9.41</v>
+        <v>9.69</v>
       </c>
       <c r="J43" t="n">
-        <v>56</v>
+        <v>291</v>
       </c>
       <c r="K43" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="L43" t="n">
-        <v>24.9</v>
+        <v>35.4</v>
       </c>
       <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>North Canna Higher Vibes Adventure Pack 5mg THC</t>
+          <t>Modist Melt Ginger Lemon Lime THC 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2247,38 +2270,45 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D44" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="E44" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
         <v>0.96</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H44" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="I44" t="n">
-        <v>15</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>135</v>
+        <v>277</v>
       </c>
       <c r="K44" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="M44" t="inlineStr"/>
+        <v>34.3</v>
+      </c>
+      <c r="L44" t="n">
+        <v>20</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine 50cs mix</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Daizy's Cream Soda 10mg THC 4pk 12oz can</t>
+          <t>North Canna Higher Vibes Adventure Pack 5mg THC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2287,28 +2317,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D45" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="E45" t="n">
-        <v>12.3</v>
+        <v>6.7</v>
       </c>
       <c r="F45" t="n">
         <v>0.96</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H45" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I45" t="n">
-        <v>10.57</v>
+        <v>15</v>
       </c>
       <c r="J45" t="n">
-        <v>127</v>
+        <v>225</v>
+      </c>
+      <c r="K45" t="n">
+        <v>34.7</v>
       </c>
       <c r="M45" t="inlineStr"/>
     </row>
@@ -2330,22 +2363,22 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>22.4</v>
+        <v>21.9</v>
       </c>
       <c r="F46" t="n">
         <v>0.96</v>
       </c>
       <c r="G46" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H46" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I46" t="n">
         <v>2.8</v>
       </c>
       <c r="J46" t="n">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="M46" t="inlineStr"/>
     </row>
@@ -2367,29 +2400,29 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="F47" t="n">
         <v>0.96</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I47" t="n">
         <v>2.8</v>
       </c>
       <c r="J47" t="n">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>North Canna High Tonics Berry Lemonade 10mg THC</t>
+          <t>Looner Root Beer 10mg THC Soda 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2398,38 +2431,35 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>19.4</v>
       </c>
       <c r="F48" t="n">
         <v>0.96</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="I48" t="n">
-        <v>9.67</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
-        <v>58</v>
-      </c>
-      <c r="K48" t="n">
-        <v>35.4</v>
+        <v>263</v>
       </c>
       <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Looner Root Beer 10mg THC Soda 12oz can</t>
+          <t>Brez Single 2.5mg THC 7.5oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2444,29 +2474,32 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>19.2</v>
+        <v>13.8</v>
       </c>
       <c r="F49" t="n">
-        <v>0.96</v>
+        <v>1.24</v>
       </c>
       <c r="G49" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="J49" t="n">
-        <v>260</v>
+        <v>220</v>
+      </c>
+      <c r="K49" t="n">
+        <v>100</v>
       </c>
       <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Brez Single 2.5mg THC 7.5oz can</t>
+          <t>Looner Sweet Orange Soda 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2481,32 +2514,29 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>14.5</v>
+        <v>17.1</v>
       </c>
       <c r="F50" t="n">
-        <v>1.24</v>
+        <v>0.96</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="H50" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I50" t="n">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
-        <v>220</v>
-      </c>
-      <c r="K50" t="n">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Looner Sweet Orange Soda 10mg THC 12oz can</t>
+          <t>Looner Pink Lemonade 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2521,29 +2551,29 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>18.2</v>
+        <v>16</v>
       </c>
       <c r="F51" t="n">
         <v>0.96</v>
       </c>
       <c r="G51" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H51" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="I51" t="n">
         <v>2.8</v>
       </c>
       <c r="J51" t="n">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Looner Pink Lemonade 10mg THC 12oz can</t>
+          <t>North Canna Higher Vibes Blueberry Citrus 5mg THC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2552,35 +2582,38 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="E52" t="n">
-        <v>18</v>
+        <v>8.1</v>
       </c>
       <c r="F52" t="n">
         <v>0.96</v>
       </c>
       <c r="G52" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="H52" t="n">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="J52" t="n">
-        <v>244</v>
+        <v>192</v>
+      </c>
+      <c r="K52" t="n">
+        <v>33.1</v>
       </c>
       <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>North Canna Higher Vibes Raspberry Lemon 5mg THC</t>
+          <t>Looner Peach Lemonade 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2589,38 +2622,35 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>8.699999999999999</v>
+        <v>15.1</v>
       </c>
       <c r="F53" t="n">
         <v>0.96</v>
       </c>
       <c r="G53" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="H53" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
-        <v>240</v>
-      </c>
-      <c r="K53" t="n">
-        <v>33.1</v>
+        <v>204</v>
       </c>
       <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Looner Peach Lemonade 10mg THC 12oz can</t>
+          <t>Looner Creme Soda 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2635,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="F54" t="n">
         <v>0.96</v>
@@ -2657,7 +2687,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Looner Creme Soda 10mg THC 12oz can</t>
+          <t>Looner Deww 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2672,29 +2702,29 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F55" t="n">
         <v>0.96</v>
       </c>
       <c r="G55" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H55" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I55" t="n">
         <v>2.8</v>
       </c>
       <c r="J55" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>North Canna Higher Vibes Blueberry Citrus 5mg THC</t>
+          <t>North Canna Higher Vibes Raspberry Lemon 5mg THC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,28 +2733,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D56" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="F56" t="n">
         <v>0.96</v>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H56" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I56" t="n">
-        <v>8.039999999999999</v>
+        <v>8</v>
       </c>
       <c r="J56" t="n">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="K56" t="n">
         <v>33.1</v>
@@ -2734,7 +2764,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Foundry Nation Two Scoops Root Beer 10mg THC 12oz can</t>
+          <t>Bent Paddle Muse Mango Citrus 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2743,35 +2773,35 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="E57" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>0.96</v>
       </c>
       <c r="G57" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="I57" t="n">
-        <v>2.21</v>
+        <v>7.33</v>
       </c>
       <c r="J57" t="n">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Looner Deww 10mg THC 12oz can</t>
+          <t>Foundry Nation Two Scoops Root Beer 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2786,29 +2816,29 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>13.3</v>
+        <v>11</v>
       </c>
       <c r="F58" t="n">
         <v>0.96</v>
       </c>
       <c r="G58" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H58" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="J58" t="n">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Bent Paddle Muse Mango Citrus 5mg THC 4pk 12oz can</t>
+          <t>Minny Grown Boat Cruise Cosmo 4pk 12oz can</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2817,16 +2847,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D59" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="E59" t="n">
-        <v>7.3</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -2835,10 +2865,10 @@
         <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>7.33</v>
+        <v>11</v>
       </c>
       <c r="J59" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="M59" t="inlineStr"/>
     </row>
@@ -2897,29 +2927,29 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="F61" t="n">
         <v>0.96</v>
       </c>
       <c r="G61" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H61" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I61" t="n">
         <v>2.8</v>
       </c>
       <c r="J61" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Collective Project Raspberry Lemonade 5mg THC 4pk 12oz can</t>
+          <t>Tempter's Strawberry 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2928,34 +2958,34 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>8.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="F62" t="n">
-        <v>1.8</v>
+        <v>0.92</v>
       </c>
       <c r="G62" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="H62" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="I62" t="n">
-        <v>8.640000000000001</v>
+        <v>2.67</v>
       </c>
       <c r="J62" t="n">
-        <v>259</v>
+        <v>144</v>
       </c>
       <c r="K62" t="n">
-        <v>44.8</v>
+        <v>37.1</v>
       </c>
       <c r="L62" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M62" t="inlineStr"/>
     </row>
@@ -2971,13 +3001,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F63" t="n">
         <v>1.8</v>
@@ -2999,7 +3029,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tempter's Strawberry 10mg THC 12oz can</t>
+          <t>IYKYK Strawberry Lemonade 10mg 12oz can</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3014,35 +3044,29 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
       <c r="F64" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="G64" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H64" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I64" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="J64" t="n">
-        <v>141</v>
-      </c>
-      <c r="K64" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="L64" t="n">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Wild State Birdie Pineapple Mango 10mg THC 4pk 12oz can</t>
+          <t>Tempter's Citrus 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3051,38 +3075,41 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="F65" t="n">
         <v>0.95</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H65" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="I65" t="n">
-        <v>9.83</v>
+        <v>2.67</v>
       </c>
       <c r="J65" t="n">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="K65" t="n">
-        <v>26.5</v>
+        <v>37.1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>22</v>
       </c>
       <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CANN Variety Pack 2mg THC 12pk 8oz can</t>
+          <t>Wild State Birdie Pineapple Mango 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3091,28 +3118,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="E66" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="F66" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="G66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I66" t="n">
-        <v>21.22</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>212</v>
+        <v>59</v>
+      </c>
+      <c r="K66" t="n">
+        <v>26.5</v>
       </c>
       <c r="M66" t="inlineStr"/>
     </row>
@@ -3134,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>12.2</v>
+        <v>10.7</v>
       </c>
       <c r="F67" t="n">
         <v>1.03</v>
@@ -3159,7 +3189,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IYKYK Strawberry Lemonade 10mg 12oz can</t>
+          <t>Looner Half and Half 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3174,29 +3204,29 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="F68" t="n">
         <v>0.96</v>
       </c>
       <c r="G68" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H68" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I68" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Tempter's Citrus 10mg THC 12oz can</t>
+          <t>Birch's Ginger Ale Seltzer 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3211,35 +3241,29 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="F69" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="G69" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H69" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I69" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>123</v>
-      </c>
-      <c r="K69" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="L69" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CANN Hi'er Boy Lemon Lavender 10mg THC 4pk 12oz can</t>
+          <t>Collective Project Raspberry Lemonade 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3248,16 +3272,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="E70" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="G70" t="n">
         <v>3</v>
@@ -3266,59 +3290,55 @@
         <v>18</v>
       </c>
       <c r="I70" t="n">
-        <v>9.43</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>170</v>
+        <v>156</v>
+      </c>
+      <c r="K70" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="L70" t="n">
+        <v>30</v>
       </c>
       <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Minny Grown Skol! 10 Pack</t>
+          <t>CANN Hi'er Boy Lemon Lavender 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Edibles</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="F71" t="n">
-        <v>1.22</v>
+        <v>0.96</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
         <v>12</v>
       </c>
       <c r="I71" t="n">
-        <v>8</v>
+        <v>9.43</v>
       </c>
       <c r="J71" t="n">
-        <v>96</v>
-      </c>
-      <c r="K71" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="L71" t="n">
-        <v>20</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3338,22 +3358,22 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="F72" t="n">
         <v>0.86</v>
       </c>
       <c r="G72" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H72" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I72" t="n">
         <v>2.67</v>
       </c>
       <c r="J72" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K72" t="n">
         <v>37.1</v>
@@ -3366,7 +3386,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Looner Half and Half 10mg THC 12oz can</t>
+          <t>CANN Variety Pack 2mg THC 12pk 8oz can</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3381,29 +3401,29 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8.9</v>
+        <v>1.6</v>
       </c>
       <c r="F73" t="n">
         <v>0.96</v>
       </c>
       <c r="G73" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H73" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>21.22</v>
       </c>
       <c r="J73" t="n">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Birch's Ginger Ale Seltzer 10mg THC 12oz can</t>
+          <t>Looner Cola 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3418,29 +3438,29 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="F74" t="n">
         <v>0.96</v>
       </c>
       <c r="G74" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H74" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CANN Hi Boy Lemon Lavender 5mg THC 4pk 12oz can</t>
+          <t>Birch's Cherry Seltzer 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3455,66 +3475,76 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="F75" t="n">
         <v>0.96</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H75" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I75" t="n">
-        <v>11.27</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>203</v>
+        <v>58</v>
       </c>
       <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Looner Cola 10mg THC 12oz can</t>
+          <t>Minny Grown Skol! 10 Pack</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Edibles</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="E76" t="n">
-        <v>8.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="F76" t="n">
-        <v>0.96</v>
+        <v>1.22</v>
       </c>
       <c r="G76" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="J76" t="n">
-        <v>112</v>
-      </c>
-      <c r="M76" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="K76" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>20</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Birch's Cherry Seltzer 10mg THC 12oz can</t>
+          <t>Foundry Nation Two Scoops Cherry 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3529,29 +3559,29 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F77" t="n">
         <v>0.96</v>
       </c>
       <c r="G77" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H77" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>3.21</v>
       </c>
       <c r="J77" t="n">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Collective Project Cherry Limade 5mg THC 4pk 12oz can</t>
+          <t>CANN Hi Boy Lemon Lavender 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3560,16 +3590,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="F78" t="n">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="G78" t="n">
         <v>2</v>
@@ -3578,23 +3608,17 @@
         <v>12</v>
       </c>
       <c r="I78" t="n">
-        <v>8.81</v>
+        <v>11.27</v>
       </c>
       <c r="J78" t="n">
-        <v>106</v>
-      </c>
-      <c r="K78" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="L78" t="n">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Foundry Nation Two Scoops Cherry 10mg THC 12oz can</t>
+          <t>Foundry Nation Two Scoops Orange 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3609,29 +3633,29 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>8.5</v>
+        <v>6.9</v>
       </c>
       <c r="F79" t="n">
         <v>0.96</v>
       </c>
       <c r="G79" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H79" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I79" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="J79" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CANN Hi Boy Blood Orange Cardamom 5mg THC 4pk 12oz can</t>
+          <t>Birch's Blueberry 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3646,29 +3670,29 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="F80" t="n">
         <v>0.96</v>
       </c>
       <c r="G80" t="n">
+        <v>24</v>
+      </c>
+      <c r="H80" t="n">
+        <v>24</v>
+      </c>
+      <c r="I80" t="n">
         <v>2</v>
       </c>
-      <c r="H80" t="n">
-        <v>12</v>
-      </c>
-      <c r="I80" t="n">
-        <v>10.62</v>
-      </c>
       <c r="J80" t="n">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IYKYK Lemonade 10mg 12oz can</t>
+          <t>CANN Hi Boy Blood Orange Cardamom 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3683,29 +3707,29 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="F81" t="n">
         <v>0.96</v>
       </c>
       <c r="G81" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I81" t="n">
-        <v>2.25</v>
+        <v>10.62</v>
       </c>
       <c r="J81" t="n">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CANN Hi'er Boy Blood Orange Cardamom 10mg THC 4pk 12oz can</t>
+          <t>CANN Hi'er Boy Ginger Lemongrass 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3720,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F82" t="n">
         <v>0.96</v>
@@ -3732,17 +3756,17 @@
         <v>12</v>
       </c>
       <c r="I82" t="n">
-        <v>10.86</v>
+        <v>12.78</v>
       </c>
       <c r="J82" t="n">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Birch's Blueberry 10mg THC 12oz can</t>
+          <t>CANN Hi'er Boy Blood Orange Cardamom 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3757,29 +3781,29 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="F83" t="n">
         <v>0.96</v>
       </c>
       <c r="G83" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H83" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>10.86</v>
       </c>
       <c r="J83" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Foundry Nation Two Scoops Orange 10mg THC 12oz can</t>
+          <t>IYKYK Peach Tea 10mg 12oz can</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3794,29 +3818,29 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="F84" t="n">
         <v>0.96</v>
       </c>
       <c r="G84" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H84" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="J84" t="n">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CANN Hi'er Boy Ginger Lemongrass 10mg THC 4pk 12oz can</t>
+          <t>IYKYK Lemonade 10mg 12oz can</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3831,29 +3855,29 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="F85" t="n">
         <v>0.96</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H85" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I85" t="n">
-        <v>12.78</v>
+        <v>2.26</v>
       </c>
       <c r="J85" t="n">
-        <v>153</v>
+        <v>50</v>
       </c>
       <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CANN Hi Boy Cranberry Sage 5mg THC</t>
+          <t>Looner Mocktail Mule 10mg THC 12oz can</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3868,22 +3892,22 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="F86" t="n">
         <v>0.96</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H86" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I86" t="n">
-        <v>11.27</v>
+        <v>2.8</v>
       </c>
       <c r="J86" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="M86" t="inlineStr"/>
     </row>
@@ -3927,7 +3951,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Looner Mocktail Mule 10mg THC 12oz can</t>
+          <t>CANN Hi Boy Cranberry Sage 5mg THC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3942,29 +3966,29 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="F88" t="n">
         <v>0.96</v>
       </c>
       <c r="G88" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H88" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>11.27</v>
       </c>
       <c r="J88" t="n">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IYKYK Peach Tea 10mg 12oz can</t>
+          <t>CANN Hi'er Boy Grapefruit Rosemary 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3979,29 +4003,29 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="F89" t="n">
         <v>0.96</v>
       </c>
       <c r="G89" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H89" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I89" t="n">
-        <v>2.24</v>
+        <v>12.78</v>
       </c>
       <c r="J89" t="n">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CANN Hi'er Boy Grapefruit Rosemary 10mg THC 4pk 12oz can</t>
+          <t>IYKYK Lemonade Tea 10mg 12oz can</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4016,22 +4040,22 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="F90" t="n">
         <v>0.96</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I90" t="n">
-        <v>12.78</v>
+        <v>2.21</v>
       </c>
       <c r="J90" t="n">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="M90" t="inlineStr"/>
     </row>
@@ -4050,25 +4074,25 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E91" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="F91" t="n">
         <v>1.11</v>
       </c>
       <c r="G91" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H91" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I91" t="n">
         <v>9.17</v>
       </c>
       <c r="J91" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K91" t="n">
         <v>33.1</v>
@@ -4078,7 +4102,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IYKYK Lemonade Tea 10mg 12oz can</t>
+          <t>CANN Hi Boy Grapefruit Rosemary 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4093,29 +4117,29 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="F92" t="n">
         <v>0.96</v>
       </c>
       <c r="G92" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I92" t="n">
-        <v>2.21</v>
+        <v>11.27</v>
       </c>
       <c r="J92" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CANN Hi Boy Grapefruit Rosemary 5mg THC 4pk 12oz can</t>
+          <t>Clrty Pineapple Hibiscus 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4130,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="F93" t="n">
-        <v>0.96</v>
+        <v>1.27</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -4142,17 +4166,17 @@
         <v>6</v>
       </c>
       <c r="I93" t="n">
-        <v>11.27</v>
+        <v>11.24</v>
       </c>
       <c r="J93" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Clrty Pineapple Hibiscus 10mg THC 4pk 12oz can</t>
+          <t>CANN Roadie Lemon Lavender 2mg THC 0.5oz</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4167,29 +4191,29 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F94" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I94" t="n">
-        <v>11.24</v>
+        <v>1.25</v>
       </c>
       <c r="J94" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Blackstack Real Trees Honeycrisp Apple 10mg THC 4pk 16oz can</t>
+          <t>Iverson Bubba Chuck Berry 10mg THC 16oz can</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4198,10 +4222,10 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0.2</v>
@@ -4210,23 +4234,23 @@
         <v>0.96</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>12.67</v>
+        <v>2.49</v>
       </c>
       <c r="J95" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CANN Roadie Lemon Lavender 2mg THC 0.5oz</t>
+          <t>Cann Roadie Grapefruit Rosemary 2mg THC 0.5oz</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4241,10 +4265,10 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F96" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -4263,7 +4287,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Iverson Bubba Chuck Berry 10mg THC 16oz can</t>
+          <t>Iverson Cran-Apple Crossover 10mg THC 16oz can</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4278,29 +4302,29 @@
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F97" t="n">
         <v>0.96</v>
       </c>
       <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J97" t="n">
         <v>2</v>
-      </c>
-      <c r="H97" t="n">
-        <v>2</v>
-      </c>
-      <c r="I97" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J97" t="n">
-        <v>5</v>
       </c>
       <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cann Roadie Grapefruit Rosemary 2mg THC 0.5oz</t>
+          <t>GRAV Pineapple Breeze 10mg THC 50ml btl</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4315,29 +4339,29 @@
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F98" t="n">
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="I98" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="J98" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Iverson Cran-Apple Crossover 10mg THC 16oz can</t>
+          <t>Iverson 96 Nectarine 10mg THC 16oz can</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4352,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
         <v>0.96</v>
@@ -4364,7 +4388,7 @@
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="J99" t="n">
         <v>2</v>
@@ -4374,7 +4398,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GRAV Pineapple Breeze 10mg THC 50ml btl</t>
+          <t>Inbound DreaMN Komodo 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4389,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
         <v>0.96</v>
@@ -4401,86 +4425,12 @@
         <v>6</v>
       </c>
       <c r="I100" t="n">
-        <v>1.84</v>
+        <v>12.5</v>
       </c>
       <c r="J100" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="M100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Iverson 96 Nectarine 10mg THC 16oz can</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="G101" t="n">
-        <v>1</v>
-      </c>
-      <c r="H101" t="n">
-        <v>1</v>
-      </c>
-      <c r="I101" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="J101" t="n">
-        <v>2</v>
-      </c>
-      <c r="M101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Inbound DreaMN Komodo 10mg 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" t="n">
-        <v>6</v>
-      </c>
-      <c r="I102" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J102" t="n">
-        <v>75</v>
-      </c>
-      <c r="M102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -913,9 +913,6 @@
       <c r="M9" t="n">
         <v>55</v>
       </c>
-      <c r="N9" t="n">
-        <v>22</v>
-      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1119,9 +1116,6 @@
       <c r="M13" t="n">
         <v>55</v>
       </c>
-      <c r="N13" t="n">
-        <v>22</v>
-      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -1273,9 +1267,6 @@
       <c r="M16" t="n">
         <v>55</v>
       </c>
-      <c r="N16" t="n">
-        <v>22</v>
-      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -1932,14 +1923,7 @@
       <c r="M29" t="n">
         <v>54</v>
       </c>
-      <c r="N29" t="n">
-        <v>20</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
     </row>
@@ -2043,14 +2027,7 @@
       <c r="M31" t="n">
         <v>42</v>
       </c>
-      <c r="N31" t="n">
-        <v>20</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2158,14 +2135,7 @@
       <c r="M33" t="n">
         <v>47</v>
       </c>
-      <c r="N33" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
     </row>
@@ -2269,14 +2239,7 @@
       <c r="M35" t="n">
         <v>54</v>
       </c>
-      <c r="N35" t="n">
-        <v>20</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
     </row>
@@ -2432,14 +2395,7 @@
       <c r="M38" t="n">
         <v>47</v>
       </c>
-      <c r="N38" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
     </row>
@@ -2491,14 +2447,7 @@
       <c r="M39" t="n">
         <v>56</v>
       </c>
-      <c r="N39" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
     </row>
@@ -2550,14 +2499,7 @@
       <c r="M40" t="n">
         <v>46</v>
       </c>
-      <c r="N40" t="n">
-        <v>20</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
@@ -2665,14 +2607,7 @@
       <c r="M42" t="n">
         <v>54</v>
       </c>
-      <c r="N42" t="n">
-        <v>20</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
     </row>
@@ -2724,14 +2659,7 @@
       <c r="M43" t="n">
         <v>47</v>
       </c>
-      <c r="N43" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
     </row>
@@ -2891,9 +2819,6 @@
       <c r="M46" t="n">
         <v>60</v>
       </c>
-      <c r="N46" t="n">
-        <v>23.1</v>
-      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
@@ -3002,14 +2927,7 @@
       <c r="M48" t="n">
         <v>39</v>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3998,14 +3916,7 @@
       <c r="M2" t="n">
         <v>42</v>
       </c>
-      <c r="N2" t="n">
-        <v>20</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
@@ -4061,14 +3972,7 @@
       <c r="M3" t="n">
         <v>46</v>
       </c>
-      <c r="N3" t="n">
-        <v>20</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
@@ -4236,14 +4140,7 @@
       <c r="M6" t="n">
         <v>39</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
@@ -4590,14 +4487,7 @@
       <c r="M6" t="n">
         <v>45</v>
       </c>
-      <c r="N6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -965,9 +965,6 @@
       <c r="M10" t="n">
         <v>55</v>
       </c>
-      <c r="N10" t="n">
-        <v>22</v>
-      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1015,9 +1012,6 @@
       <c r="M11" t="n">
         <v>55</v>
       </c>
-      <c r="N11" t="n">
-        <v>22</v>
-      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1268,9 +1262,6 @@
       <c r="M16" t="n">
         <v>55</v>
       </c>
-      <c r="N16" t="n">
-        <v>22</v>
-      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -1932,14 +1923,7 @@
       <c r="M29" t="n">
         <v>42</v>
       </c>
-      <c r="N29" t="n">
-        <v>20</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
@@ -1995,14 +1979,7 @@
       <c r="M30" t="n">
         <v>47</v>
       </c>
-      <c r="N30" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
     </row>
@@ -2054,14 +2031,7 @@
       <c r="M31" t="n">
         <v>47</v>
       </c>
-      <c r="N31" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -2165,11 +2135,7 @@
       <c r="M33" t="n">
         <v>48</v>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
     </row>
@@ -2273,14 +2239,7 @@
       <c r="M35" t="n">
         <v>47</v>
       </c>
-      <c r="N35" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
     </row>
@@ -2384,14 +2343,7 @@
       <c r="M37" t="n">
         <v>46</v>
       </c>
-      <c r="N37" t="n">
-        <v>20</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2447,14 +2399,7 @@
       <c r="M38" t="n">
         <v>54</v>
       </c>
-      <c r="N38" t="n">
-        <v>20</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
     </row>
@@ -2506,14 +2451,7 @@
       <c r="M39" t="n">
         <v>54</v>
       </c>
-      <c r="N39" t="n">
-        <v>20</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
     </row>
@@ -2673,14 +2611,7 @@
       <c r="M42" t="n">
         <v>54</v>
       </c>
-      <c r="N42" t="n">
-        <v>20</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
     </row>
@@ -2784,11 +2715,7 @@
       <c r="M44" t="n">
         <v>42</v>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3673,14 +3600,7 @@
       <c r="M2" t="n">
         <v>42</v>
       </c>
-      <c r="N2" t="n">
-        <v>20</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
@@ -3736,14 +3656,7 @@
       <c r="M3" t="n">
         <v>46</v>
       </c>
-      <c r="N3" t="n">
-        <v>20</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
@@ -3855,11 +3768,7 @@
       <c r="M5" t="n">
         <v>42</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
@@ -4206,14 +4115,7 @@
       <c r="M6" t="n">
         <v>45</v>
       </c>
-      <c r="N6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -965,9 +965,6 @@
       <c r="M10" t="n">
         <v>55</v>
       </c>
-      <c r="N10" t="n">
-        <v>22</v>
-      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1067,9 +1064,6 @@
       <c r="M12" t="n">
         <v>55</v>
       </c>
-      <c r="N12" t="n">
-        <v>22</v>
-      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1268,9 +1262,6 @@
       <c r="M16" t="n">
         <v>55</v>
       </c>
-      <c r="N16" t="n">
-        <v>22</v>
-      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -1984,14 +1975,7 @@
       <c r="M30" t="n">
         <v>42</v>
       </c>
-      <c r="N30" t="n">
-        <v>20</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2047,14 +2031,7 @@
       <c r="M31" t="n">
         <v>47</v>
       </c>
-      <c r="N31" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -2106,14 +2083,7 @@
       <c r="M32" t="n">
         <v>47</v>
       </c>
-      <c r="N32" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -2321,14 +2291,7 @@
       <c r="M36" t="n">
         <v>47</v>
       </c>
-      <c r="N36" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
     </row>
@@ -2380,14 +2343,7 @@
       <c r="M37" t="n">
         <v>54</v>
       </c>
-      <c r="N37" t="n">
-        <v>20</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
     </row>
@@ -2439,11 +2395,7 @@
       <c r="M38" t="n">
         <v>48</v>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
     </row>
@@ -2495,14 +2447,7 @@
       <c r="M39" t="n">
         <v>46</v>
       </c>
-      <c r="N39" t="n">
-        <v>20</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2558,14 +2503,7 @@
       <c r="M40" t="n">
         <v>54</v>
       </c>
-      <c r="N40" t="n">
-        <v>20</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
     </row>
@@ -2669,14 +2607,7 @@
       <c r="M42" t="n">
         <v>54</v>
       </c>
-      <c r="N42" t="n">
-        <v>20</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
     </row>
@@ -2780,14 +2711,7 @@
       <c r="M44" t="n">
         <v>39</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3832,14 +3756,7 @@
       <c r="M2" t="n">
         <v>42</v>
       </c>
-      <c r="N2" t="n">
-        <v>20</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
@@ -3895,14 +3812,7 @@
       <c r="M3" t="n">
         <v>46</v>
       </c>
-      <c r="N3" t="n">
-        <v>20</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
@@ -3958,14 +3868,7 @@
       <c r="M4" t="n">
         <v>39</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
@@ -4368,14 +4271,7 @@
       <c r="M6" t="n">
         <v>45</v>
       </c>
-      <c r="N6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -965,6 +965,9 @@
       <c r="M10" t="n">
         <v>55</v>
       </c>
+      <c r="N10" t="n">
+        <v>22</v>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1064,6 +1067,9 @@
       <c r="M12" t="n">
         <v>55</v>
       </c>
+      <c r="N12" t="n">
+        <v>22</v>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1262,6 +1268,9 @@
       <c r="M16" t="n">
         <v>55</v>
       </c>
+      <c r="N16" t="n">
+        <v>22</v>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -1975,7 +1984,14 @@
       <c r="M30" t="n">
         <v>42</v>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>20</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine 50cs mix</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2031,7 +2047,14 @@
       <c r="M31" t="n">
         <v>47</v>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -2083,7 +2106,14 @@
       <c r="M32" t="n">
         <v>47</v>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -2291,7 +2321,14 @@
       <c r="M36" t="n">
         <v>47</v>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Kiwi Strawberry (Pink)</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
     </row>
@@ -2343,7 +2380,14 @@
       <c r="M37" t="n">
         <v>54</v>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>20</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
     </row>
@@ -2395,7 +2439,11 @@
       <c r="M38" t="n">
         <v>48</v>
       </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
     </row>
@@ -2447,7 +2495,14 @@
       <c r="M39" t="n">
         <v>46</v>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>20</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine 100cs Buy</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2503,7 +2558,14 @@
       <c r="M40" t="n">
         <v>54</v>
       </c>
-      <c r="O40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>20</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
     </row>
@@ -2607,7 +2669,14 @@
       <c r="M42" t="n">
         <v>54</v>
       </c>
-      <c r="O42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>20</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
     </row>
@@ -2711,7 +2780,14 @@
       <c r="M44" t="n">
         <v>39</v>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3756,7 +3832,14 @@
       <c r="M2" t="n">
         <v>42</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine 50cs mix</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
@@ -3812,7 +3895,14 @@
       <c r="M3" t="n">
         <v>46</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine 100cs Buy</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
@@ -3868,7 +3958,14 @@
       <c r="M4" t="n">
         <v>39</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
@@ -4271,7 +4368,14 @@
       <c r="M6" t="n">
         <v>45</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:S74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,55 +452,65 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -534,29 +544,35 @@
         <v>-4.3</v>
       </c>
       <c r="G2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>8</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>6</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>52</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>46</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,7 +602,7 @@
         <v>-4.3</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -595,20 +611,26 @@
         <v>6</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>9</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>54</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>44</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -638,7 +660,7 @@
         <v>-2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -647,20 +669,26 @@
         <v>8</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>23.07</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>185</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>48</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -690,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -699,20 +727,26 @@
         <v>149</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>149</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>149</v>
+      </c>
+      <c r="M5" t="n">
         <v>8</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>1192</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>43</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -742,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -751,20 +785,26 @@
         <v>96</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>96</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
+        <v>96</v>
+      </c>
+      <c r="M6" t="n">
         <v>2.8</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>269</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>53</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -794,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -803,20 +843,26 @@
         <v>93</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>93</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>93</v>
+      </c>
+      <c r="M7" t="n">
         <v>2.8</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>260</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>53</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -846,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -855,20 +901,26 @@
         <v>89</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>89</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
+        <v>89</v>
+      </c>
+      <c r="M8" t="n">
         <v>2.8</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>249</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>53</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -898,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -907,20 +959,26 @@
         <v>87</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>87</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
+        <v>87</v>
+      </c>
+      <c r="M9" t="n">
         <v>2.8</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>244</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>53</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -950,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -959,20 +1017,26 @@
         <v>69</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>69</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
+        <v>69</v>
+      </c>
+      <c r="M10" t="n">
         <v>2.8</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>193</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>53</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1002,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1011,20 +1075,26 @@
         <v>68</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>68</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
+        <v>68</v>
+      </c>
+      <c r="M11" t="n">
         <v>2.8</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>190</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>53</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1054,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>-9</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1063,20 +1133,26 @@
         <v>65</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>65</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
+        <v>65</v>
+      </c>
+      <c r="M12" t="n">
         <v>2.8</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>182</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>53</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1106,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1115,20 +1191,26 @@
         <v>62</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>62</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>62</v>
+      </c>
+      <c r="M13" t="n">
         <v>2.8</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>174</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>53</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1153,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1162,20 +1244,26 @@
         <v>42</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>42</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
+        <v>42</v>
+      </c>
+      <c r="M14" t="n">
         <v>2.25</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>94</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>62</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1200,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>47</v>
+        <v>-8</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1209,23 +1297,26 @@
         <v>47</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>47</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
+        <v>47</v>
+      </c>
+      <c r="M15" t="n">
         <v>2.67</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>126</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>55</v>
       </c>
-      <c r="N15" t="n">
-        <v>22</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1255,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1264,20 +1355,26 @@
         <v>44</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>44</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
+        <v>44</v>
+      </c>
+      <c r="M16" t="n">
         <v>2.8</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>123</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>53</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1307,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>44</v>
+        <v>-17</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1316,20 +1413,26 @@
         <v>44</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>44</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
+        <v>44</v>
+      </c>
+      <c r="M17" t="n">
         <v>2.8</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>123</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>53</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1359,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>43</v>
+        <v>-12</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1368,20 +1471,26 @@
         <v>43</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>43</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
+        <v>43</v>
+      </c>
+      <c r="M18" t="n">
         <v>2.8</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>120</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>53</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1406,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>41</v>
+        <v>-7</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1415,23 +1524,26 @@
         <v>41</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>41</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
+        <v>41</v>
+      </c>
+      <c r="M19" t="n">
         <v>2.67</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>110</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>55</v>
       </c>
-      <c r="N19" t="n">
-        <v>22</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1461,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1470,20 +1582,26 @@
         <v>38</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>38</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
+        <v>38</v>
+      </c>
+      <c r="M20" t="n">
         <v>2.8</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>106</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>53</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1513,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1522,20 +1640,26 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>26</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
+        <v>26</v>
+      </c>
+      <c r="M21" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>52</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>67</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1565,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1574,20 +1698,26 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>26</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
+        <v>26</v>
+      </c>
+      <c r="M22" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>52</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>67</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1617,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>25</v>
+        <v>-40</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1626,20 +1756,26 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>25</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
+        <v>25</v>
+      </c>
+      <c r="M23" t="n">
         <v>1.91</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>48</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>68</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1669,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1678,20 +1814,26 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>24</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
+        <v>24</v>
+      </c>
+      <c r="M24" t="n">
         <v>2</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>48</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>67</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1716,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>-20</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1725,23 +1867,26 @@
         <v>30</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>30</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
+        <v>30</v>
+      </c>
+      <c r="M25" t="n">
         <v>2.67</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>80</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>55</v>
       </c>
-      <c r="N25" t="n">
-        <v>22</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1771,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1780,20 +1925,26 @@
         <v>31</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>31</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
+        <v>31</v>
+      </c>
+      <c r="M26" t="n">
         <v>2.8</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>87</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>53</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1818,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1827,20 +1978,26 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>24</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
+        <v>24</v>
+      </c>
+      <c r="M27" t="n">
         <v>2.21</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>53</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>63</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1874,20 +2031,26 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>22</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
+        <v>22</v>
+      </c>
+      <c r="M28" t="n">
         <v>2.24</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>63</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1912,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>-9</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1921,20 +2084,26 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>20</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
+        <v>20</v>
+      </c>
+      <c r="M29" t="n">
         <v>2.25</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>45</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>62</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1964,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>-18</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1973,20 +2142,26 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>20</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
+        <v>20</v>
+      </c>
+      <c r="M30" t="n">
         <v>2.86</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>57</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>52</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2016,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>-71</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2025,20 +2200,26 @@
         <v>9</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
+        <v>9</v>
+      </c>
+      <c r="M31" t="n">
         <v>3.25</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>29</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>46</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2068,7 +2249,7 @@
         <v>1.4</v>
       </c>
       <c r="G32" t="n">
-        <v>30</v>
+        <v>-15</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2077,27 +2258,26 @@
         <v>30</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>30</v>
+      </c>
+      <c r="L32" t="n">
         <v>5</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>276</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>42</v>
       </c>
-      <c r="N32" t="n">
-        <v>20</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
         <is>
           <t>New item - set quantity by hand</t>
         </is>
@@ -2131,36 +2311,35 @@
         <v>1.5</v>
       </c>
       <c r="G33" t="n">
+        <v>62</v>
+      </c>
+      <c r="H33" t="n">
+        <v>42</v>
+      </c>
+      <c r="I33" t="n">
         <v>169</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>25</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>144</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>24</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>5.91</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>851</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>46</v>
       </c>
-      <c r="N33" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2190,36 +2369,35 @@
         <v>2.1</v>
       </c>
       <c r="G34" t="n">
+        <v>41</v>
+      </c>
+      <c r="H34" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="I34" t="n">
         <v>119</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>28</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>90</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>15</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>5.83</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>525</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>47</v>
       </c>
-      <c r="N34" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2249,29 +2427,35 @@
         <v>2.4</v>
       </c>
       <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="I35" t="n">
         <v>136</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>10</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>126</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>21</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>11.2</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>1411</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>50</v>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2301,29 +2485,35 @@
         <v>2.6</v>
       </c>
       <c r="G36" t="n">
+        <v>9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I36" t="n">
         <v>100</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>25</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>76</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>38</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>22.5</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>1710</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>48</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2353,29 +2543,35 @@
         <v>2.6</v>
       </c>
       <c r="G37" t="n">
+        <v>129</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>115</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>28</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>84</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>14</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>11.2</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>941</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>50</v>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2405,29 +2601,35 @@
         <v>2.6</v>
       </c>
       <c r="G38" t="n">
+        <v>131</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>99</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>18</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>84</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>14</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>11.2</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>941</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>50</v>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2457,36 +2659,35 @@
         <v>2.7</v>
       </c>
       <c r="G39" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H39" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I39" t="n">
         <v>59</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>15</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>42</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>7</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>10</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>420</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>47</v>
       </c>
-      <c r="N39" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2516,29 +2717,35 @@
         <v>3</v>
       </c>
       <c r="G40" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="I40" t="n">
         <v>81</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>17</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>66</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>11</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>11.2</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>739</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>50</v>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2568,29 +2775,35 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I41" t="n">
         <v>28</v>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>15</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>12</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>37.71</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>453</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>-170</v>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -2624,36 +2837,35 @@
         <v>3.1</v>
       </c>
       <c r="G42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>82</v>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>40</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>42</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>21</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>14</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>588</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>39</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
         <is>
           <t>New item - set quantity by hand</t>
         </is>
@@ -2687,29 +2899,35 @@
         <v>3.1</v>
       </c>
       <c r="G43" t="n">
+        <v>118</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>36</v>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>8</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>30</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>11.2</v>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
         <v>336</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>50</v>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2739,36 +2957,35 @@
         <v>3.1</v>
       </c>
       <c r="G44" t="n">
+        <v>200</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>12</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>8</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>6</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>10.67</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>64</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>33</v>
       </c>
-      <c r="N44" t="n">
-        <v>20</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2798,29 +3015,35 @@
         <v>3.2</v>
       </c>
       <c r="G45" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="I45" t="n">
         <v>77</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>20</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>60</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>10</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>11.2</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>672</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>50</v>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2850,29 +3073,35 @@
         <v>3.2</v>
       </c>
       <c r="G46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>51</v>
+      </c>
+      <c r="I46" t="n">
         <v>71</v>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>18</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>54</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>9</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>11.2</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>605</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>50</v>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2902,29 +3131,35 @@
         <v>3.2</v>
       </c>
       <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
         <v>54</v>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>24</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>30</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>5</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>11.2</v>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>336</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>50</v>
       </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2954,32 +3189,35 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
+        <v>19</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
         <v>36</v>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>12</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>24</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>4</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>18.33</v>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
         <v>440</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>44</v>
       </c>
-      <c r="N48" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3009,29 +3247,35 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
+        <v>19</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>25</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>4</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>20</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>10</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>20.5</v>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>410</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>49</v>
       </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3061,36 +3305,35 @@
         <v>3.6</v>
       </c>
       <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>123</v>
+      </c>
+      <c r="I50" t="n">
         <v>89</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>46</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>48</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>4</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>8</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>384</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>54</v>
       </c>
-      <c r="N50" t="n">
-        <v>20</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3120,29 +3363,35 @@
         <v>3.6</v>
       </c>
       <c r="G51" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="I51" t="n">
         <v>117</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>99</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>18</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>3</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>8</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>144</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>54</v>
       </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3172,29 +3421,35 @@
         <v>3.6</v>
       </c>
       <c r="G52" t="n">
+        <v>13</v>
+      </c>
+      <c r="H52" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I52" t="n">
         <v>44</v>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>24</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>18</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>3</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>11.2</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>202</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>50</v>
       </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3224,29 +3479,35 @@
         <v>3.6</v>
       </c>
       <c r="G53" t="n">
+        <v>-61</v>
+      </c>
+      <c r="H53" t="n">
+        <v>15</v>
+      </c>
+      <c r="I53" t="n">
         <v>7</v>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>6</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>43.45</v>
       </c>
-      <c r="L53" t="n">
+      <c r="N53" t="n">
         <v>261</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>-211</v>
       </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -3280,36 +3541,35 @@
         <v>3.7</v>
       </c>
       <c r="G54" t="n">
+        <v>18</v>
+      </c>
+      <c r="H54" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="I54" t="n">
         <v>63</v>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>37</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>24</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>2</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>8</v>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
         <v>192</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>54</v>
       </c>
-      <c r="N54" t="n">
-        <v>20</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3339,33 +3599,35 @@
         <v>3.8</v>
       </c>
       <c r="G55" t="n">
+        <v>6</v>
+      </c>
+      <c r="H55" t="n">
+        <v>25</v>
+      </c>
+      <c r="I55" t="n">
         <v>21</v>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>4</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>16</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>8</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>24.78</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>396</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>48</v>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3395,32 +3657,35 @@
         <v>3.8</v>
       </c>
       <c r="G56" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I56" t="n">
         <v>59</v>
       </c>
-      <c r="H56" t="n">
+      <c r="J56" t="n">
         <v>49</v>
       </c>
-      <c r="I56" t="n">
+      <c r="K56" t="n">
         <v>12</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>12.17</v>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
         <v>146</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>45</v>
       </c>
-      <c r="N56" t="n">
-        <v>17</v>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3450,29 +3715,35 @@
         <v>3.9</v>
       </c>
       <c r="G57" t="n">
+        <v>4</v>
+      </c>
+      <c r="H57" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="I57" t="n">
         <v>44</v>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>28</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>18</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>3</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>11.2</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>202</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>50</v>
       </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3502,29 +3773,35 @@
         <v>3.9</v>
       </c>
       <c r="G58" t="n">
+        <v>29</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>27</v>
       </c>
-      <c r="H58" t="n">
+      <c r="J58" t="n">
         <v>8</v>
       </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>18</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>3</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>11.2</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>202</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>50</v>
       </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3554,7 +3831,7 @@
         <v>3.9</v>
       </c>
       <c r="G59" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3563,20 +3840,26 @@
         <v>6</v>
       </c>
       <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>6</v>
+      </c>
+      <c r="L59" t="n">
         <v>3</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
         <v>10.05</v>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>60</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>82</v>
       </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3606,29 +3889,35 @@
         <v>3.9</v>
       </c>
       <c r="G60" t="n">
+        <v>52</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>28</v>
       </c>
-      <c r="H60" t="n">
+      <c r="J60" t="n">
         <v>15</v>
       </c>
-      <c r="I60" t="n">
+      <c r="K60" t="n">
         <v>12</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>2</v>
       </c>
-      <c r="K60" t="n">
+      <c r="M60" t="n">
         <v>11.2</v>
       </c>
-      <c r="L60" t="n">
+      <c r="N60" t="n">
         <v>134</v>
       </c>
-      <c r="M60" t="n">
+      <c r="O60" t="n">
         <v>50</v>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3658,29 +3947,35 @@
         <v>3.9</v>
       </c>
       <c r="G61" t="n">
+        <v>-66</v>
+      </c>
+      <c r="H61" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I61" t="n">
         <v>14</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>5</v>
       </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>9</v>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>3</v>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
         <v>47.08</v>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>424</v>
       </c>
-      <c r="M61" t="n">
+      <c r="O61" t="n">
         <v>-52</v>
       </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -3714,29 +4009,35 @@
         <v>5.4</v>
       </c>
       <c r="G62" t="n">
+        <v>15</v>
+      </c>
+      <c r="H62" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I62" t="n">
         <v>76</v>
       </c>
-      <c r="H62" t="n">
+      <c r="J62" t="n">
         <v>65</v>
       </c>
-      <c r="I62" t="n">
+      <c r="K62" t="n">
         <v>12</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>2</v>
       </c>
-      <c r="K62" t="n">
+      <c r="M62" t="n">
         <v>9.75</v>
       </c>
-      <c r="L62" t="n">
+      <c r="N62" t="n">
         <v>117</v>
       </c>
-      <c r="M62" t="n">
+      <c r="O62" t="n">
         <v>49</v>
       </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3766,29 +4067,35 @@
         <v>6.8</v>
       </c>
       <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="I63" t="n">
         <v>47</v>
       </c>
-      <c r="H63" t="n">
+      <c r="J63" t="n">
         <v>43</v>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>6</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>1</v>
       </c>
-      <c r="K63" t="n">
+      <c r="M63" t="n">
         <v>9.75</v>
       </c>
-      <c r="L63" t="n">
+      <c r="N63" t="n">
         <v>58</v>
       </c>
-      <c r="M63" t="n">
+      <c r="O63" t="n">
         <v>49</v>
       </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3818,29 +4125,35 @@
         <v>6.8</v>
       </c>
       <c r="G64" t="n">
+        <v>17</v>
+      </c>
+      <c r="H64" t="n">
+        <v>35</v>
+      </c>
+      <c r="I64" t="n">
         <v>63</v>
       </c>
-      <c r="H64" t="n">
+      <c r="J64" t="n">
         <v>56</v>
       </c>
-      <c r="I64" t="n">
+      <c r="K64" t="n">
         <v>6</v>
       </c>
-      <c r="J64" t="n">
+      <c r="L64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="n">
+      <c r="M64" t="n">
         <v>9.75</v>
       </c>
-      <c r="L64" t="n">
+      <c r="N64" t="n">
         <v>58</v>
       </c>
-      <c r="M64" t="n">
+      <c r="O64" t="n">
         <v>49</v>
       </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3870,29 +4183,35 @@
         <v>9.9</v>
       </c>
       <c r="G65" t="n">
+        <v>18</v>
+      </c>
+      <c r="H65" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I65" t="n">
         <v>31</v>
       </c>
-      <c r="H65" t="n">
+      <c r="J65" t="n">
         <v>22</v>
       </c>
-      <c r="I65" t="n">
+      <c r="K65" t="n">
         <v>12</v>
       </c>
-      <c r="J65" t="n">
+      <c r="L65" t="n">
         <v>2</v>
       </c>
-      <c r="K65" t="n">
+      <c r="M65" t="n">
         <v>8.67</v>
       </c>
-      <c r="L65" t="n">
+      <c r="N65" t="n">
         <v>104</v>
       </c>
-      <c r="M65" t="n">
+      <c r="O65" t="n">
         <v>50</v>
       </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3922,29 +4241,35 @@
         <v>13.9</v>
       </c>
       <c r="G66" t="n">
+        <v>25</v>
+      </c>
+      <c r="H66" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I66" t="n">
         <v>235</v>
       </c>
-      <c r="H66" t="n">
+      <c r="J66" t="n">
         <v>46</v>
       </c>
-      <c r="I66" t="n">
+      <c r="K66" t="n">
         <v>192</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>32</v>
       </c>
-      <c r="K66" t="n">
+      <c r="M66" t="n">
         <v>9.84</v>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
         <v>1889</v>
       </c>
-      <c r="M66" t="n">
+      <c r="O66" t="n">
         <v>48</v>
       </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3974,29 +4299,35 @@
         <v>14.5</v>
       </c>
       <c r="G67" t="n">
+        <v>20</v>
+      </c>
+      <c r="H67" t="n">
+        <v>31</v>
+      </c>
+      <c r="I67" t="n">
         <v>37</v>
       </c>
-      <c r="H67" t="n">
+      <c r="J67" t="n">
         <v>29</v>
       </c>
-      <c r="I67" t="n">
+      <c r="K67" t="n">
         <v>6</v>
       </c>
-      <c r="J67" t="n">
+      <c r="L67" t="n">
         <v>1</v>
       </c>
-      <c r="K67" t="n">
+      <c r="M67" t="n">
         <v>9.75</v>
       </c>
-      <c r="L67" t="n">
+      <c r="N67" t="n">
         <v>59</v>
       </c>
-      <c r="M67" t="n">
+      <c r="O67" t="n">
         <v>49</v>
       </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4026,29 +4357,35 @@
         <v>17.1</v>
       </c>
       <c r="G68" t="n">
+        <v>27</v>
+      </c>
+      <c r="H68" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I68" t="n">
         <v>22</v>
       </c>
-      <c r="H68" t="n">
+      <c r="J68" t="n">
         <v>9</v>
       </c>
-      <c r="I68" t="n">
+      <c r="K68" t="n">
         <v>12</v>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
         <v>2</v>
       </c>
-      <c r="K68" t="n">
+      <c r="M68" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="L68" t="n">
+      <c r="N68" t="n">
         <v>118</v>
       </c>
-      <c r="M68" t="n">
+      <c r="O68" t="n">
         <v>48</v>
       </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4078,29 +4415,35 @@
         <v>17.5</v>
       </c>
       <c r="G69" t="n">
+        <v>17</v>
+      </c>
+      <c r="H69" t="n">
         <v>11</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
+        <v>11</v>
+      </c>
+      <c r="J69" t="n">
         <v>4</v>
       </c>
-      <c r="I69" t="n">
+      <c r="K69" t="n">
         <v>6</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="n">
+      <c r="M69" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>53</v>
       </c>
-      <c r="M69" t="n">
+      <c r="O69" t="n">
         <v>49</v>
       </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4130,29 +4473,35 @@
         <v>22.6</v>
       </c>
       <c r="G70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I70" t="n">
         <v>75</v>
       </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
         <v>66</v>
       </c>
-      <c r="I70" t="n">
+      <c r="K70" t="n">
         <v>12</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>2</v>
       </c>
-      <c r="K70" t="n">
+      <c r="M70" t="n">
         <v>9.81</v>
       </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
         <v>118</v>
       </c>
-      <c r="M70" t="n">
+      <c r="O70" t="n">
         <v>48</v>
       </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4182,29 +4531,35 @@
         <v>28.6</v>
       </c>
       <c r="G71" t="n">
+        <v>8</v>
+      </c>
+      <c r="H71" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I71" t="n">
         <v>17</v>
       </c>
-      <c r="H71" t="n">
+      <c r="J71" t="n">
         <v>9</v>
       </c>
-      <c r="I71" t="n">
+      <c r="K71" t="n">
         <v>6</v>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="n">
+      <c r="M71" t="n">
         <v>8.76</v>
       </c>
-      <c r="L71" t="n">
+      <c r="N71" t="n">
         <v>53</v>
       </c>
-      <c r="M71" t="n">
+      <c r="O71" t="n">
         <v>50</v>
       </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4234,29 +4589,35 @@
         <v>29.5</v>
       </c>
       <c r="G72" t="n">
+        <v>9</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I72" t="n">
         <v>8</v>
       </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>6</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="n">
+      <c r="M72" t="n">
         <v>9</v>
       </c>
-      <c r="L72" t="n">
+      <c r="N72" t="n">
         <v>54</v>
       </c>
-      <c r="M72" t="n">
+      <c r="O72" t="n">
         <v>49</v>
       </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4286,29 +4647,35 @@
         <v>38.6</v>
       </c>
       <c r="G73" t="n">
+        <v>42</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I73" t="n">
         <v>5</v>
       </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
         <v>6</v>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" t="n">
+      <c r="M73" t="n">
         <v>9.15</v>
       </c>
-      <c r="L73" t="n">
+      <c r="N73" t="n">
         <v>55</v>
       </c>
-      <c r="M73" t="n">
+      <c r="O73" t="n">
         <v>48</v>
       </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4338,29 +4705,35 @@
         <v>39</v>
       </c>
       <c r="G74" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H74" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I74" t="n">
         <v>23</v>
       </c>
-      <c r="H74" t="n">
+      <c r="J74" t="n">
         <v>16</v>
       </c>
-      <c r="I74" t="n">
+      <c r="K74" t="n">
         <v>6</v>
       </c>
-      <c r="J74" t="n">
+      <c r="L74" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="n">
+      <c r="M74" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="L74" t="n">
+      <c r="N74" t="n">
         <v>59</v>
       </c>
-      <c r="M74" t="n">
+      <c r="O74" t="n">
         <v>48</v>
       </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4373,7 +4746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4409,55 +4782,65 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -4491,7 +4874,7 @@
         <v>1.4</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>-15</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -4500,27 +4883,26 @@
         <v>30</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>276</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>42</v>
       </c>
-      <c r="N2" t="n">
-        <v>20</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>New item - set quantity by hand</t>
         </is>
@@ -4554,29 +4936,35 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I3" t="n">
         <v>28</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>15</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>37.71</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>453</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>-170</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -4610,36 +4998,35 @@
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>82</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>40</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>42</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>21</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>14</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>588</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>39</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>New item - set quantity by hand</t>
         </is>
@@ -4673,29 +5060,35 @@
         <v>3.6</v>
       </c>
       <c r="G5" t="n">
+        <v>-61</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" t="n">
         <v>7</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>43.45</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>261</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>-211</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -4729,29 +5122,35 @@
         <v>3.9</v>
       </c>
       <c r="G6" t="n">
+        <v>-66</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I6" t="n">
         <v>14</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>9</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>47.08</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>424</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>-52</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -4768,7 +5167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4804,45 +5203,55 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
@@ -4876,27 +5285,33 @@
         <v>0.9</v>
       </c>
       <c r="G2" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H2" t="n">
+        <v>18</v>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>6</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>12.67</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>76</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>44</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4926,27 +5341,33 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="I3" t="n">
         <v>55</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>48</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>2.83</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>136</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>48</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4976,27 +5397,33 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>38</v>
+      </c>
+      <c r="H4" t="n">
+        <v>52</v>
+      </c>
+      <c r="I4" t="n">
         <v>91</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>96</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>2.29</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>220</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>58</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5026,27 +5453,33 @@
         <v>0.8</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="I5" t="n">
         <v>17</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>18</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>11</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>198</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>45</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5076,34 +5509,33 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
+        <v>-36</v>
+      </c>
+      <c r="H6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I6" t="n">
         <v>32</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>19</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>12</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>11</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>132</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>45</v>
       </c>
-      <c r="N6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5133,27 +5565,33 @@
         <v>3</v>
       </c>
       <c r="G7" t="n">
+        <v>-51</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I7" t="n">
         <v>7</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>10.01</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>60</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>47</v>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1087,9 +1087,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1312,9 +1309,6 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
-      <c r="P15" t="n">
-        <v>22</v>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -1716,9 +1710,6 @@
       <c r="O22" t="n">
         <v>55</v>
       </c>
-      <c r="P22" t="n">
-        <v>22</v>
-      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -2110,14 +2101,7 @@
       <c r="O29" t="n">
         <v>42</v>
       </c>
-      <c r="P29" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
@@ -2179,14 +2163,7 @@
       <c r="O30" t="n">
         <v>47</v>
       </c>
-      <c r="P30" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
@@ -2302,14 +2279,7 @@
       <c r="O32" t="n">
         <v>46</v>
       </c>
-      <c r="P32" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
@@ -2483,14 +2453,7 @@
       <c r="O35" t="n">
         <v>47</v>
       </c>
-      <c r="P35" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2958,14 +2921,7 @@
       <c r="O43" t="n">
         <v>54</v>
       </c>
-      <c r="P43" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3022,9 +2978,6 @@
       </c>
       <c r="O44" t="n">
         <v>44</v>
-      </c>
-      <c r="P44" t="n">
-        <v>25.2</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -3084,14 +3037,7 @@
       <c r="O45" t="n">
         <v>39</v>
       </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
@@ -3269,14 +3215,7 @@
       <c r="O48" t="n">
         <v>54</v>
       </c>
-      <c r="P48" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3334,11 +3273,7 @@
       <c r="O49" t="n">
         <v>48</v>
       </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
     </row>
@@ -3570,11 +3505,7 @@
       <c r="O53" t="n">
         <v>48</v>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
@@ -4575,14 +4506,7 @@
       <c r="O2" t="n">
         <v>42</v>
       </c>
-      <c r="P2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -4706,14 +4630,7 @@
       <c r="O4" t="n">
         <v>39</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -4775,11 +4692,7 @@
       <c r="O5" t="n">
         <v>48</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -5414,14 +5327,7 @@
       <c r="O6" t="n">
         <v>45</v>
       </c>
-      <c r="P6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1203,9 +1203,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1312,9 +1309,6 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
-      <c r="P15" t="n">
-        <v>22</v>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -1769,9 +1763,6 @@
       <c r="O23" t="n">
         <v>55</v>
       </c>
-      <c r="P23" t="n">
-        <v>22</v>
-      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -2110,14 +2101,7 @@
       <c r="O29" t="n">
         <v>42</v>
       </c>
-      <c r="P29" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
@@ -2179,14 +2163,7 @@
       <c r="O30" t="n">
         <v>47</v>
       </c>
-      <c r="P30" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
@@ -2360,14 +2337,7 @@
       <c r="O33" t="n">
         <v>46</v>
       </c>
-      <c r="P33" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
     </row>
@@ -2599,14 +2569,7 @@
       <c r="O37" t="n">
         <v>47</v>
       </c>
-      <c r="P37" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
@@ -2664,14 +2627,7 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="P38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -3081,14 +3037,7 @@
       <c r="O45" t="n">
         <v>39</v>
       </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
@@ -3149,9 +3098,6 @@
       </c>
       <c r="O46" t="n">
         <v>44</v>
-      </c>
-      <c r="P46" t="n">
-        <v>25.2</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3211,14 +3157,7 @@
       <c r="O47" t="n">
         <v>54</v>
       </c>
-      <c r="P47" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3566,11 +3505,7 @@
       <c r="O53" t="n">
         <v>48</v>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
@@ -3690,14 +3625,7 @@
       <c r="O55" t="n">
         <v>45</v>
       </c>
-      <c r="P55" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
@@ -4698,14 +4626,7 @@
       <c r="O2" t="n">
         <v>42</v>
       </c>
-      <c r="P2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 50cs mix</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -4829,14 +4750,7 @@
       <c r="O4" t="n">
         <v>39</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -4898,11 +4812,7 @@
       <c r="O5" t="n">
         <v>48</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -4964,14 +4874,7 @@
       <c r="O6" t="n">
         <v>45</v>
       </c>
-      <c r="P6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
@@ -5606,14 +5509,7 @@
       <c r="O6" t="n">
         <v>45</v>
       </c>
-      <c r="P6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1203,6 +1203,9 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
+      <c r="P13" t="n">
+        <v>22</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1256,6 +1259,9 @@
       <c r="O14" t="n">
         <v>55</v>
       </c>
+      <c r="P14" t="n">
+        <v>22</v>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -1536,6 +1542,9 @@
       <c r="O19" t="n">
         <v>55</v>
       </c>
+      <c r="P19" t="n">
+        <v>22</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -2101,7 +2110,14 @@
       <c r="O29" t="n">
         <v>42</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine 50cs mix</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
@@ -2163,7 +2179,14 @@
       <c r="O30" t="n">
         <v>47</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
@@ -2221,7 +2244,14 @@
       <c r="O31" t="n">
         <v>46</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
@@ -2279,7 +2309,14 @@
       <c r="O32" t="n">
         <v>47</v>
       </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Kiwi Strawberry (Pink)</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
@@ -2453,7 +2490,14 @@
       <c r="O35" t="n">
         <v>46</v>
       </c>
-      <c r="Q35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine 100cs Buy</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
@@ -2631,7 +2675,14 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="Q38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2921,7 +2972,14 @@
       <c r="O43" t="n">
         <v>39</v>
       </c>
-      <c r="Q43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
@@ -3099,6 +3157,9 @@
       <c r="O46" t="n">
         <v>44</v>
       </c>
+      <c r="P46" t="n">
+        <v>25.2</v>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3215,7 +3276,14 @@
       <c r="O48" t="n">
         <v>45</v>
       </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
@@ -3276,6 +3344,9 @@
       </c>
       <c r="O49" t="n">
         <v>60</v>
+      </c>
+      <c r="P49" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -4278,7 +4349,14 @@
       <c r="O2" t="n">
         <v>42</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine 50cs mix</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -4340,7 +4418,14 @@
       <c r="O3" t="n">
         <v>46</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine 100cs Buy</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -4402,7 +4487,14 @@
       <c r="O4" t="n">
         <v>39</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -4464,7 +4556,14 @@
       <c r="O5" t="n">
         <v>45</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -4525,6 +4624,9 @@
       </c>
       <c r="O6" t="n">
         <v>60</v>
+      </c>
+      <c r="P6" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -5161,7 +5263,14 @@
       <c r="O6" t="n">
         <v>45</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,6 +1145,9 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
+      <c r="P12" t="n">
+        <v>22</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1309,6 +1312,9 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
+      <c r="P15" t="n">
+        <v>22</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -1816,6 +1822,9 @@
       <c r="O24" t="n">
         <v>55</v>
       </c>
+      <c r="P24" t="n">
+        <v>22</v>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
@@ -2336,6 +2345,9 @@
       <c r="O33" t="n">
         <v>43</v>
       </c>
+      <c r="P33" t="n">
+        <v>22</v>
+      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -2625,6 +2637,9 @@
       <c r="O38" t="n">
         <v>60</v>
       </c>
+      <c r="P38" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
@@ -2811,6 +2826,9 @@
       <c r="O41" t="n">
         <v>60</v>
       </c>
+      <c r="P41" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -2927,6 +2945,9 @@
       <c r="O43" t="n">
         <v>44</v>
       </c>
+      <c r="P43" t="n">
+        <v>25.2</v>
+      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3159,7 +3180,14 @@
       <c r="O47" t="n">
         <v>54</v>
       </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3333,7 +3361,14 @@
       <c r="O50" t="n">
         <v>46</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3449,9 +3484,12 @@
       <c r="O52" t="n">
         <v>42</v>
       </c>
+      <c r="P52" t="n">
+        <v>20</v>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
         </is>
       </c>
       <c r="R52" t="inlineStr"/>
@@ -3693,9 +3731,12 @@
       <c r="O56" t="n">
         <v>42</v>
       </c>
+      <c r="P56" t="n">
+        <v>19.7</v>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
         </is>
       </c>
       <c r="R56" t="inlineStr"/>
@@ -4299,6 +4340,9 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
+      <c r="P5" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -4485,9 +4529,12 @@
       <c r="O8" t="n">
         <v>42</v>
       </c>
+      <c r="P8" t="n">
+        <v>20</v>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -4613,9 +4660,12 @@
       <c r="O10" t="n">
         <v>42</v>
       </c>
+      <c r="P10" t="n">
+        <v>19.7</v>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1317,9 +1314,6 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
-      <c r="P15" t="n">
-        <v>22</v>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -1764,9 +1758,6 @@
       <c r="O23" t="n">
         <v>55</v>
       </c>
-      <c r="P23" t="n">
-        <v>22</v>
-      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -2403,9 +2394,6 @@
       <c r="O34" t="n">
         <v>43</v>
       </c>
-      <c r="P34" t="n">
-        <v>22</v>
-      </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -2753,11 +2741,7 @@
       <c r="O40" t="n">
         <v>47</v>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2873,9 +2857,6 @@
       <c r="O42" t="n">
         <v>60</v>
       </c>
-      <c r="P42" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
@@ -3062,14 +3043,7 @@
       <c r="O45" t="n">
         <v>54</v>
       </c>
-      <c r="P45" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3243,9 +3217,6 @@
       <c r="O48" t="n">
         <v>44</v>
       </c>
-      <c r="P48" t="n">
-        <v>25.2</v>
-      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -3304,12 +3275,9 @@
       <c r="O49" t="n">
         <v>40</v>
       </c>
-      <c r="P49" t="n">
-        <v>18.3</v>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Buy a pallet, get 9cs of Gummies Free to hit invoice net of $47</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R49" t="inlineStr"/>
@@ -3427,12 +3395,9 @@
       <c r="O51" t="n">
         <v>42</v>
       </c>
-      <c r="P51" t="n">
-        <v>20</v>
-      </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr"/>
@@ -3674,12 +3639,9 @@
       <c r="O55" t="n">
         <v>42</v>
       </c>
-      <c r="P55" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R55" t="inlineStr"/>
@@ -4283,9 +4245,6 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -4472,12 +4431,9 @@
       <c r="O8" t="n">
         <v>42</v>
       </c>
-      <c r="P8" t="n">
-        <v>20</v>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -4603,12 +4559,9 @@
       <c r="O10" t="n">
         <v>42</v>
       </c>
-      <c r="P10" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1370,9 +1367,6 @@
       <c r="O16" t="n">
         <v>55</v>
       </c>
-      <c r="P16" t="n">
-        <v>22</v>
-      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -1653,9 +1647,6 @@
       <c r="O21" t="n">
         <v>55</v>
       </c>
-      <c r="P21" t="n">
-        <v>22</v>
-      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
@@ -2345,9 +2336,6 @@
       <c r="O33" t="n">
         <v>43</v>
       </c>
-      <c r="P33" t="n">
-        <v>22</v>
-      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -2522,14 +2510,7 @@
       <c r="O36" t="n">
         <v>54</v>
       </c>
-      <c r="P36" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2761,11 +2742,7 @@
       <c r="O40" t="n">
         <v>47</v>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2943,9 +2920,6 @@
       <c r="O43" t="n">
         <v>44</v>
       </c>
-      <c r="P43" t="n">
-        <v>25.2</v>
-      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3004,14 +2978,7 @@
       <c r="O44" t="n">
         <v>54</v>
       </c>
-      <c r="P44" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
@@ -3243,14 +3210,7 @@
       <c r="O48" t="n">
         <v>45</v>
       </c>
-      <c r="P48" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
@@ -3369,9 +3329,6 @@
       <c r="O50" t="n">
         <v>60</v>
       </c>
-      <c r="P50" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
@@ -3492,12 +3449,9 @@
       <c r="O52" t="n">
         <v>40</v>
       </c>
-      <c r="P52" t="n">
-        <v>18.3</v>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Buy a pallet, get 9cs of Gummies Free to hit invoice net of $47</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr"/>
@@ -3615,12 +3569,9 @@
       <c r="O54" t="n">
         <v>43</v>
       </c>
-      <c r="P54" t="n">
-        <v>20</v>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R54" t="inlineStr"/>
@@ -3862,12 +3813,9 @@
       <c r="O58" t="n">
         <v>42</v>
       </c>
-      <c r="P58" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R58" t="inlineStr"/>
@@ -4538,14 +4486,7 @@
       <c r="O5" t="n">
         <v>45</v>
       </c>
-      <c r="P5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -4664,9 +4605,6 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
-      <c r="P7" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -4729,12 +4667,9 @@
       <c r="O8" t="n">
         <v>43</v>
       </c>
-      <c r="P8" t="n">
-        <v>20</v>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -4860,12 +4795,9 @@
       <c r="O10" t="n">
         <v>42</v>
       </c>
-      <c r="P10" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -5564,9 +5496,6 @@
       <c r="O6" t="n">
         <v>46</v>
       </c>
-      <c r="P6" t="n">
-        <v>52.7</v>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1370,9 +1367,6 @@
       <c r="O16" t="n">
         <v>55</v>
       </c>
-      <c r="P16" t="n">
-        <v>22</v>
-      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -1653,9 +1647,6 @@
       <c r="O21" t="n">
         <v>55</v>
       </c>
-      <c r="P21" t="n">
-        <v>22</v>
-      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
@@ -2345,9 +2336,6 @@
       <c r="O33" t="n">
         <v>43</v>
       </c>
-      <c r="P33" t="n">
-        <v>22</v>
-      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -2642,9 +2630,6 @@
       <c r="O38" t="n">
         <v>60</v>
       </c>
-      <c r="P38" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
@@ -2765,11 +2750,7 @@
       <c r="O40" t="n">
         <v>47</v>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -3000,14 +2981,7 @@
       <c r="O44" t="n">
         <v>54</v>
       </c>
-      <c r="P44" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
@@ -3064,9 +3038,6 @@
       </c>
       <c r="O45" t="n">
         <v>60</v>
-      </c>
-      <c r="P45" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -3126,14 +3097,7 @@
       <c r="O46" t="n">
         <v>45</v>
       </c>
-      <c r="P46" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
@@ -3144,12 +3108,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gigli 10mg THC Variety Pack 12pk 12oz can</t>
+          <t>Gigli Extra Gigli Variety 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>199284006881</t>
+          <t>643459380004</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3163,58 +3127,51 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>659</v>
+        <v>371</v>
       </c>
       <c r="F47" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="G47" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="I47" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="J47" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="K47" t="n">
+        <v>12</v>
+      </c>
+      <c r="L47" t="n">
         <v>2</v>
       </c>
-      <c r="L47" t="n">
-        <v>1</v>
-      </c>
       <c r="M47" t="n">
-        <v>26.1</v>
+        <v>9.75</v>
       </c>
       <c r="N47" t="n">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="O47" t="n">
-        <v>40</v>
-      </c>
-      <c r="P47" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w); Buy a pallet, get 9cs of Gummies Free to hit invoice net of $47</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gigli Extra Gigli Variety 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blueberry Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>643459380004</t>
+          <t>643459379992</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3228,22 +3185,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>371</v>
+        <v>324</v>
       </c>
       <c r="F48" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="G48" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="H48" t="n">
-        <v>81.8</v>
+        <v>44.5</v>
       </c>
       <c r="I48" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J48" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K48" t="n">
         <v>12</v>
@@ -3267,12 +3224,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Climbing Kites Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Gigli Blood Orange Margarita 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>850047906380</t>
+          <t>643459380028</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3282,66 +3239,55 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Global Reserve LLC</t>
+          <t>Gigli MN LLC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>125</v>
+        <v>372</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="G49" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I49" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="J49" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="K49" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>14.71</v>
+        <v>9.75</v>
       </c>
       <c r="N49" t="n">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="O49" t="n">
-        <v>43</v>
-      </c>
-      <c r="P49" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>New item - set quantity by hand</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Gigli Blueberry Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>643459379992</t>
+          <t>643459379909</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3355,22 +3301,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="F50" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
       <c r="G50" t="n">
-        <v>-3</v>
+        <v>30</v>
       </c>
       <c r="H50" t="n">
-        <v>44.5</v>
+        <v>20.8</v>
       </c>
       <c r="I50" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="K50" t="n">
         <v>12</v>
@@ -3379,27 +3325,31 @@
         <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>9.75</v>
+        <v>8.67</v>
       </c>
       <c r="N50" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="O50" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Overstocked (8 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gigli Blood Orange Margarita 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blueberry Lemonade 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>643459380028</t>
+          <t>643459379947</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3413,22 +3363,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>372</v>
+        <v>292</v>
       </c>
       <c r="F51" t="n">
-        <v>7.3</v>
+        <v>20.2</v>
       </c>
       <c r="G51" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H51" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="I51" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="J51" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>12</v>
@@ -3437,27 +3387,31 @@
         <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>9.75</v>
+        <v>8.74</v>
       </c>
       <c r="N51" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="O51" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
+          <t>Gigli Blood Orange Margarita 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>643459379909</t>
+          <t>643459379916</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3471,22 +3425,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="F52" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="G52" t="n">
-        <v>30</v>
+        <v>-5</v>
       </c>
       <c r="H52" t="n">
-        <v>20.8</v>
+        <v>11</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J52" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>12</v>
@@ -3495,31 +3449,31 @@
         <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>8.67</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O52" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Overstocked (8 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (21 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Utepils Happy Pack 10mg THC 12pk 12oz can</t>
+          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>852449007429</t>
+          <t>198168611401</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3529,66 +3483,59 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Gigli MN LLC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="F53" t="n">
-        <v>9.199999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="G53" t="n">
-        <v>10</v>
+        <v>-8</v>
       </c>
       <c r="H53" t="n">
-        <v>28.2</v>
+        <v>17</v>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="J53" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>24.81</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="O53" t="n">
-        <v>42</v>
-      </c>
-      <c r="P53" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Overstocked (9 wks on hand) - confirm before buying more; Seasonal - last year ~28/wk vs 19 now, buy ahead?</t>
+          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~17/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gigli Blueberry Lemonade 5mg THC 4pk 12oz can</t>
+          <t>Gigli Pineapple Mojito 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>643459379947</t>
+          <t>643459380035</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3602,55 +3549,55 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>292</v>
+        <v>365</v>
       </c>
       <c r="F54" t="n">
-        <v>20.2</v>
+        <v>22.7</v>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H54" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>8.74</v>
+        <v>9.82</v>
       </c>
       <c r="N54" t="n">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="O54" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (23 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gigli Blood Orange Margarita 5mg THC 4pk 12oz can</t>
+          <t>Gigli Raspberry Ginger Mule 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>643459379916</t>
+          <t>643459379961</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3664,34 +3611,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="F55" t="n">
-        <v>21</v>
+        <v>28.5</v>
       </c>
       <c r="G55" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="I55" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>8.859999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="O55" t="n">
         <v>49</v>
@@ -3699,192 +3646,6 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
-        <is>
-          <t>Overstocked (21 wks on hand) - confirm before buying more</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>198168611401</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Gigli MN LLC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>189</v>
-      </c>
-      <c r="F56" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G56" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H56" t="n">
-        <v>17</v>
-      </c>
-      <c r="I56" t="n">
-        <v>98</v>
-      </c>
-      <c r="J56" t="n">
-        <v>90</v>
-      </c>
-      <c r="K56" t="n">
-        <v>6</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N56" t="n">
-        <v>59</v>
-      </c>
-      <c r="O56" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~17/wk vs 8 now, buy ahead?</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Gigli Pineapple Mojito 10mg THC 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>643459380035</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Gigli MN LLC</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>365</v>
-      </c>
-      <c r="F57" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G57" t="n">
-        <v>5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I57" t="n">
-        <v>6</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>6</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="N57" t="n">
-        <v>59</v>
-      </c>
-      <c r="O57" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>Overstocked (23 wks on hand) - confirm before buying more</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Gigli Raspberry Ginger Mule 5mg THC 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>643459379961</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Gigli MN LLC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>259</v>
-      </c>
-      <c r="F58" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G58" t="n">
-        <v>5</v>
-      </c>
-      <c r="H58" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I58" t="n">
-        <v>12</v>
-      </c>
-      <c r="J58" t="n">
-        <v>6</v>
-      </c>
-      <c r="K58" t="n">
-        <v>6</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="N58" t="n">
-        <v>54</v>
-      </c>
-      <c r="O58" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr">
         <is>
           <t>Overstocked (28 wks on hand) - confirm before buying more</t>
         </is>
@@ -3901,7 +3662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4241,9 +4002,6 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -4363,14 +4121,7 @@
       <c r="O7" t="n">
         <v>45</v>
       </c>
-      <c r="P7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
@@ -4381,12 +4132,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Climbing Kites Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>850047906380</t>
+          <t>643459379909</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4396,66 +4147,59 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Global Reserve LLC</t>
+          <t>Gigli MN LLC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>125</v>
+        <v>311</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>14.71</v>
+        <v>8.67</v>
       </c>
       <c r="N8" t="n">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="O8" t="n">
-        <v>43</v>
-      </c>
-      <c r="P8" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>New item - set quantity by hand</t>
+          <t>Overstocked (8 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
+          <t>Gigli Blueberry Lemonade 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>643459379909</t>
+          <t>643459379947</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4469,22 +4213,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="F9" t="n">
-        <v>8.4</v>
+        <v>20.2</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>20.8</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>12</v>
@@ -4493,10 +4237,10 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>8.67</v>
+        <v>8.74</v>
       </c>
       <c r="N9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O9" t="n">
         <v>50</v>
@@ -4505,19 +4249,19 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Overstocked (8 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Utepils Happy Pack 10mg THC 12pk 12oz can</t>
+          <t>Gigli Blood Orange Margarita 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>852449007429</t>
+          <t>643459379916</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4527,66 +4271,59 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Gigli MN LLC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>171</v>
+        <v>279</v>
       </c>
       <c r="F10" t="n">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="H10" t="n">
-        <v>28.2</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>12</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>24.81</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="O10" t="n">
-        <v>42</v>
-      </c>
-      <c r="P10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Overstocked (9 wks on hand) - confirm before buying more; Seasonal - last year ~28/wk vs 19 now, buy ahead?</t>
+          <t>Overstocked (21 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gigli Blueberry Lemonade 5mg THC 4pk 12oz can</t>
+          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>643459379947</t>
+          <t>198168611401</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4600,55 +4337,55 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="F11" t="n">
-        <v>20.2</v>
+        <v>22.5</v>
       </c>
       <c r="G11" t="n">
-        <v>22</v>
+        <v>-8</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>8.74</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="O11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~17/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gigli Blood Orange Margarita 5mg THC 4pk 12oz can</t>
+          <t>Gigli Pineapple Mojito 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>643459379916</t>
+          <t>643459380035</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4662,55 +4399,55 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>279</v>
+        <v>365</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>22.7</v>
       </c>
       <c r="G12" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>17.8</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>8.859999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="N12" t="n">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="O12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Overstocked (21 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (23 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Gigli Raspberry Ginger Mule 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>198168611401</t>
+          <t>643459379961</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4724,22 +4461,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="F13" t="n">
-        <v>22.5</v>
+        <v>28.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
@@ -4748,141 +4485,17 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="O13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
-        <is>
-          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~17/wk vs 8 now, buy ahead?</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Gigli Pineapple Mojito 10mg THC 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>643459380035</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Gigli MN LLC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>365</v>
-      </c>
-      <c r="F14" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="N14" t="n">
-        <v>59</v>
-      </c>
-      <c r="O14" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Overstocked (23 wks on hand) - confirm before buying more</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Gigli Raspberry Ginger Mule 5mg THC 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>643459379961</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Gigli MN LLC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>259</v>
-      </c>
-      <c r="F15" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="N15" t="n">
-        <v>54</v>
-      </c>
-      <c r="O15" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
         <is>
           <t>Overstocked (28 wks on hand) - confirm before buying more</t>
         </is>
@@ -4899,7 +4512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5216,12 +4829,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Foundry Nation Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Gigli Raspberry Tea 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>810012693882</t>
+          <t>198168016879</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5231,60 +4844,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Discontinued</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>14.5</v>
+        <v>12.4</v>
       </c>
       <c r="G6" t="n">
-        <v>-22</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>14.5</v>
+        <v>22.8</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>248</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>216</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="M6" t="n">
-        <v>18.03</v>
+        <v>9.83</v>
       </c>
       <c r="N6" t="n">
-        <v>72</v>
+        <v>2124</v>
       </c>
       <c r="O6" t="n">
-        <v>46</v>
-      </c>
-      <c r="P6" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gigli Raspberry Tea 10mg THC 4pk 12oz can</t>
+          <t>Minny Grown Boat Cruise Cosmo 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>198168016879</t>
+          <t>860009899322</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5294,53 +4900,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Discontinued</t>
+          <t>Minny Grown</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>-52</v>
       </c>
       <c r="H7" t="n">
-        <v>22.8</v>
+        <v>28.8</v>
       </c>
       <c r="I7" t="n">
-        <v>248</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>216</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>9.83</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>2124</v>
+        <v>66</v>
       </c>
       <c r="O7" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Minny Grown Boat Cruise Cosmo 4pk 12oz can</t>
+          <t>Vibes Mango Hybrid 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>860009899322</t>
+          <t>649275846564</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5350,23 +4956,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Minny Grown</t>
+          <t>Discontinued</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>-52</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
-        <v>28.8</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -5378,71 +4984,15 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>8.57</v>
       </c>
       <c r="N8" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="O8" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="Q8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Vibes Mango Hybrid 5mg THC 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>649275846564</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Discontinued</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>200</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="N9" t="n">
-        <v>51</v>
-      </c>
-      <c r="O9" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1428,9 +1425,6 @@
       <c r="O17" t="n">
         <v>55</v>
       </c>
-      <c r="P17" t="n">
-        <v>22</v>
-      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -1600,9 +1594,6 @@
       <c r="O20" t="n">
         <v>55</v>
       </c>
-      <c r="P20" t="n">
-        <v>22</v>
-      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -2755,14 +2746,7 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="P40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2819,9 +2803,6 @@
       </c>
       <c r="O41" t="n">
         <v>44</v>
-      </c>
-      <c r="P41" t="n">
-        <v>25.2</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -3063,11 +3044,7 @@
       <c r="O45" t="n">
         <v>48</v>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3794,9 +3771,6 @@
       </c>
       <c r="O57" t="n">
         <v>69</v>
-      </c>
-      <c r="P57" t="n">
-        <v>6.2</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4781,9 +4755,6 @@
       <c r="O15" t="n">
         <v>69</v>
       </c>
-      <c r="P15" t="n">
-        <v>6.2</v>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>ON AD - Sunday special (buy to 8w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:S60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1145,6 +1145,9 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
+      <c r="P12" t="n">
+        <v>22</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1425,6 +1428,9 @@
       <c r="O17" t="n">
         <v>55</v>
       </c>
+      <c r="P17" t="n">
+        <v>22</v>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -1594,6 +1600,9 @@
       <c r="O20" t="n">
         <v>55</v>
       </c>
+      <c r="P20" t="n">
+        <v>22</v>
+      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -2746,7 +2755,14 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="Q40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2803,6 +2819,9 @@
       </c>
       <c r="O41" t="n">
         <v>44</v>
+      </c>
+      <c r="P41" t="n">
+        <v>25.2</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -3044,19 +3063,23 @@
       <c r="O45" t="n">
         <v>48</v>
       </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Gigli Extra Gigli Variety 10mg THC 4pk 12oz can</t>
+          <t>Uncle Arnie's Blueberry Nightcap 10mg THC 2oz</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>643459380004</t>
+          <t>850039736483</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3066,55 +3089,66 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>Capitol Beverage Sales, L.P.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>366</v>
+        <v>1192</v>
       </c>
       <c r="F46" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="G46" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H46" t="n">
-        <v>77</v>
+        <v>444.5</v>
       </c>
       <c r="I46" t="n">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="J46" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="K46" t="n">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M46" t="n">
-        <v>9.75</v>
+        <v>1.67</v>
       </c>
       <c r="N46" t="n">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="O46" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q46" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="P46" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Seasonal - last year ~444/wk vs 283 now, buy ahead?</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gigli Blueberry Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Gigli Extra Gigli Variety 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>643459379992</t>
+          <t>643459380004</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3128,22 +3162,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="F47" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H47" t="n">
-        <v>40.2</v>
+        <v>77</v>
       </c>
       <c r="I47" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J47" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K47" t="n">
         <v>12</v>
@@ -3167,12 +3201,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gigli Blood Orange Margarita 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blueberry Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>643459380028</t>
+          <t>643459379992</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3186,34 +3220,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>372</v>
+        <v>337</v>
       </c>
       <c r="F48" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="H48" t="n">
-        <v>31</v>
+        <v>40.2</v>
       </c>
       <c r="I48" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="J48" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
         <v>9.75</v>
       </c>
       <c r="N48" t="n">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="O48" t="n">
         <v>49</v>
@@ -3225,12 +3259,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
+          <t>Fetch Zero Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>643459379909</t>
+          <t>628719778142</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3240,26 +3274,26 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>Capitol Beverage Sales, L.P.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>321</v>
+        <v>60</v>
       </c>
       <c r="F49" t="n">
-        <v>9.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="G49" t="n">
-        <v>13</v>
+        <v>-18</v>
       </c>
       <c r="H49" t="n">
-        <v>24.2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K49" t="n">
         <v>12</v>
@@ -3268,31 +3302,38 @@
         <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>8.67</v>
+        <v>6.21</v>
       </c>
       <c r="N49" t="n">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="O49" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="P49" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
+          <t>New item - set quantity by hand</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Gigli Raspberry Ginger Mule 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blood Orange Margarita 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>643459379954</t>
+          <t>643459380028</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3306,22 +3347,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F50" t="n">
-        <v>18.9</v>
+        <v>7.8</v>
       </c>
       <c r="G50" t="n">
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
-        <v>36.2</v>
+        <v>31</v>
       </c>
       <c r="I50" t="n">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="J50" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="K50" t="n">
         <v>6</v>
@@ -3333,28 +3374,24 @@
         <v>9.75</v>
       </c>
       <c r="N50" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O50" t="n">
         <v>49</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>Overstocked (19 wks on hand) - confirm before buying more; Seasonal - last year ~36/wk vs 20 now, buy ahead?</t>
-        </is>
-      </c>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gigli Blueberry Lemonade 5mg THC 4pk 12oz can</t>
+          <t>Bent Paddle Puff Party Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>643459379947</t>
+          <t>858106004268</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3364,59 +3401,63 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>Bent Paddle Brewing Co</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>284</v>
+        <v>44</v>
       </c>
       <c r="F51" t="n">
-        <v>20.3</v>
+        <v>9.4</v>
       </c>
       <c r="G51" t="n">
-        <v>15</v>
+        <v>-41</v>
       </c>
       <c r="H51" t="n">
-        <v>9.5</v>
+        <v>1.2</v>
       </c>
       <c r="I51" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J51" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>8.74</v>
+        <v>22.66</v>
       </c>
       <c r="N51" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="O51" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (9 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>198168611401</t>
+          <t>643459379909</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3430,22 +3471,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>184</v>
+        <v>321</v>
       </c>
       <c r="F52" t="n">
-        <v>21.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>-8</v>
+        <v>13</v>
       </c>
       <c r="H52" t="n">
-        <v>16.5</v>
+        <v>24.2</v>
       </c>
       <c r="I52" t="n">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="J52" t="n">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="K52" t="n">
         <v>12</v>
@@ -3454,31 +3495,31 @@
         <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>9.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="N52" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="O52" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~16/wk vs 8 now, buy ahead?</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gigli Blood Orange Margarita 5mg THC 4pk 12oz can</t>
+          <t>Acre Ginger Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>643459379916</t>
+          <t>615867915949</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3488,59 +3529,66 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>56 Brewing</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="F53" t="n">
-        <v>22.4</v>
+        <v>10.3</v>
       </c>
       <c r="G53" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I53" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>8.85</v>
+        <v>7.94</v>
       </c>
       <c r="N53" t="n">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="O53" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="P53" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Overstocked (22 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gigli Raspberry Ginger Mule 5mg THC 4pk 12oz can</t>
+          <t>Gigli Raspberry Ginger Mule 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>643459379961</t>
+          <t>643459379954</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3554,22 +3602,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>263</v>
+        <v>384</v>
       </c>
       <c r="F54" t="n">
-        <v>24.5</v>
+        <v>18.9</v>
       </c>
       <c r="G54" t="n">
-        <v>18</v>
+        <v>-7</v>
       </c>
       <c r="H54" t="n">
-        <v>4.2</v>
+        <v>36.2</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
         <v>6</v>
@@ -3578,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>8.91</v>
+        <v>9.75</v>
       </c>
       <c r="N54" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="O54" t="n">
         <v>49</v>
@@ -3590,19 +3638,19 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Overstocked (24 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (19 wks on hand) - confirm before buying more; Seasonal - last year ~36/wk vs 20 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gigli Citrus Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blueberry Lemonade 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>643459379305</t>
+          <t>643459379947</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3616,55 +3664,55 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="F55" t="n">
-        <v>25.2</v>
+        <v>20.3</v>
       </c>
       <c r="G55" t="n">
-        <v>-26</v>
+        <v>15</v>
       </c>
       <c r="H55" t="n">
-        <v>15.2</v>
+        <v>9.5</v>
       </c>
       <c r="I55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>9.77</v>
+        <v>8.74</v>
       </c>
       <c r="N55" t="n">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="O55" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Overstocked (25 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gigli Pineapple Mojito 10mg THC 4pk 12oz can</t>
+          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>643459380035</t>
+          <t>198168611401</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3678,34 +3726,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>360</v>
+        <v>184</v>
       </c>
       <c r="F56" t="n">
-        <v>25.7</v>
+        <v>21.9</v>
       </c>
       <c r="G56" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="H56" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="I56" t="n">
+        <v>103</v>
+      </c>
+      <c r="J56" t="n">
+        <v>93</v>
+      </c>
+      <c r="K56" t="n">
         <v>12</v>
       </c>
-      <c r="J56" t="n">
-        <v>6</v>
-      </c>
-      <c r="K56" t="n">
-        <v>6</v>
-      </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>9.82</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N56" t="n">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="O56" t="n">
         <v>48</v>
@@ -3714,19 +3762,19 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Overstocked (26 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~16/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Brez 5mg THC Shots 2oz</t>
+          <t>Gigli Blood Orange Margarita 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>860012637768</t>
+          <t>643459379916</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3736,49 +3784,231 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Gigli MN LLC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1097</v>
+        <v>288</v>
       </c>
       <c r="F57" t="n">
-        <v>26</v>
+        <v>22.4</v>
       </c>
       <c r="G57" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I57" t="n">
+        <v>11</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>12</v>
       </c>
-      <c r="H57" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="I57" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>48</v>
-      </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>2.5</v>
+        <v>8.85</v>
       </c>
       <c r="N57" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="O57" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 8w)</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
+        <is>
+          <t>Overstocked (22 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Gigli Raspberry Ginger Mule 5mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>643459379961</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Gigli MN LLC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>263</v>
+      </c>
+      <c r="F58" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>18</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4</v>
+      </c>
+      <c r="K58" t="n">
+        <v>6</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="N58" t="n">
+        <v>53</v>
+      </c>
+      <c r="O58" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Overstocked (24 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gigli Citrus Seltzer 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>643459379305</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Gigli MN LLC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>312</v>
+      </c>
+      <c r="F59" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H59" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I59" t="n">
+        <v>14</v>
+      </c>
+      <c r="J59" t="n">
+        <v>10</v>
+      </c>
+      <c r="K59" t="n">
+        <v>6</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="N59" t="n">
+        <v>59</v>
+      </c>
+      <c r="O59" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Overstocked (25 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gigli Pineapple Mojito 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>643459380035</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Gigli MN LLC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>360</v>
+      </c>
+      <c r="F60" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H60" t="n">
+        <v>19</v>
+      </c>
+      <c r="I60" t="n">
+        <v>12</v>
+      </c>
+      <c r="J60" t="n">
+        <v>6</v>
+      </c>
+      <c r="K60" t="n">
+        <v>6</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="N60" t="n">
+        <v>59</v>
+      </c>
+      <c r="O60" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
         <is>
           <t>Overstocked (26 wks on hand) - confirm before buying more</t>
         </is>
@@ -3795,7 +4025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4208,12 +4438,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
+          <t>Uncle Arnie's Blueberry Nightcap 10mg THC 2oz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>643459379909</t>
+          <t>850039736483</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4223,59 +4453,66 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>Capitol Beverage Sales, L.P.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>321</v>
+        <v>1192</v>
       </c>
       <c r="F7" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>-3</v>
       </c>
       <c r="H7" t="n">
-        <v>24.2</v>
+        <v>444.5</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>8.67</v>
+        <v>1.67</v>
       </c>
       <c r="N7" t="n">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="O7" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="P7" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
+          <t>Seasonal - last year ~444/wk vs 283 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gigli Raspberry Ginger Mule 10mg THC 4pk 12oz can</t>
+          <t>Fetch Zero Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>643459379954</t>
+          <t>628719778142</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4285,59 +4522,66 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>Capitol Beverage Sales, L.P.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>384</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>18.9</v>
+        <v>7.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-7</v>
+        <v>-18</v>
       </c>
       <c r="H8" t="n">
-        <v>36.2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>9.75</v>
+        <v>6.21</v>
       </c>
       <c r="N8" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="O8" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="P8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Overstocked (19 wks on hand) - confirm before buying more; Seasonal - last year ~36/wk vs 20 now, buy ahead?</t>
+          <t>New item - set quantity by hand</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gigli Blueberry Lemonade 5mg THC 4pk 12oz can</t>
+          <t>Bent Paddle Puff Party Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>643459379947</t>
+          <t>858106004268</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4347,59 +4591,63 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>Bent Paddle Brewing Co</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>284</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>20.3</v>
+        <v>9.4</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>-41</v>
       </c>
       <c r="H9" t="n">
-        <v>9.5</v>
+        <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>8.74</v>
+        <v>22.66</v>
       </c>
       <c r="N9" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="O9" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (9 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>198168611401</t>
+          <t>643459379909</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4413,22 +4661,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>184</v>
+        <v>321</v>
       </c>
       <c r="F10" t="n">
-        <v>21.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-8</v>
+        <v>13</v>
       </c>
       <c r="H10" t="n">
-        <v>16.5</v>
+        <v>24.2</v>
       </c>
       <c r="I10" t="n">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
         <v>12</v>
@@ -4437,31 +4685,31 @@
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>9.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="N10" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="O10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~16/wk vs 8 now, buy ahead?</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gigli Blood Orange Margarita 5mg THC 4pk 12oz can</t>
+          <t>Acre Ginger Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>643459379916</t>
+          <t>615867915949</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4471,59 +4719,66 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>56 Brewing</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="F11" t="n">
-        <v>22.4</v>
+        <v>10.3</v>
       </c>
       <c r="G11" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>8.85</v>
+        <v>7.94</v>
       </c>
       <c r="N11" t="n">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="O11" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="P11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Overstocked (22 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gigli Raspberry Ginger Mule 5mg THC 4pk 12oz can</t>
+          <t>Gigli Raspberry Ginger Mule 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>643459379961</t>
+          <t>643459379954</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4537,22 +4792,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>263</v>
+        <v>384</v>
       </c>
       <c r="F12" t="n">
-        <v>24.5</v>
+        <v>18.9</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>-7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>36.2</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
         <v>6</v>
@@ -4561,10 +4816,10 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>8.91</v>
+        <v>9.75</v>
       </c>
       <c r="N12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="O12" t="n">
         <v>49</v>
@@ -4573,19 +4828,19 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Overstocked (24 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (19 wks on hand) - confirm before buying more; Seasonal - last year ~36/wk vs 20 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gigli Citrus Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blueberry Lemonade 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>643459379305</t>
+          <t>643459379947</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4599,55 +4854,55 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="F13" t="n">
-        <v>25.2</v>
+        <v>20.3</v>
       </c>
       <c r="G13" t="n">
-        <v>-26</v>
+        <v>15</v>
       </c>
       <c r="H13" t="n">
-        <v>15.2</v>
+        <v>9.5</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>9.77</v>
+        <v>8.74</v>
       </c>
       <c r="N13" t="n">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="O13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Overstocked (25 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gigli Pineapple Mojito 10mg THC 4pk 12oz can</t>
+          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>643459380035</t>
+          <t>198168611401</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4661,34 +4916,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>360</v>
+        <v>184</v>
       </c>
       <c r="F14" t="n">
-        <v>25.7</v>
+        <v>21.9</v>
       </c>
       <c r="G14" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="I14" t="n">
+        <v>103</v>
+      </c>
+      <c r="J14" t="n">
+        <v>93</v>
+      </c>
+      <c r="K14" t="n">
         <v>12</v>
       </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>9.82</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="O14" t="n">
         <v>48</v>
@@ -4697,19 +4952,19 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Overstocked (26 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~16/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brez 5mg THC Shots 2oz</t>
+          <t>Gigli Blood Orange Margarita 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>860012637768</t>
+          <t>643459379916</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4719,49 +4974,231 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Gigli MN LLC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1097</v>
+        <v>288</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>22.4</v>
       </c>
       <c r="G15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>12</v>
       </c>
-      <c r="H15" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>48</v>
-      </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5</v>
+        <v>8.85</v>
       </c>
       <c r="N15" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="O15" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 8w)</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
+        <is>
+          <t>Overstocked (22 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gigli Raspberry Ginger Mule 5mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>643459379961</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Gigli MN LLC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>263</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="N16" t="n">
+        <v>53</v>
+      </c>
+      <c r="O16" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Overstocked (24 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gigli Citrus Seltzer 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>643459379305</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gigli MN LLC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>312</v>
+      </c>
+      <c r="F17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>14</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="N17" t="n">
+        <v>59</v>
+      </c>
+      <c r="O17" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Overstocked (25 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gigli Pineapple Mojito 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>643459380035</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Gigli MN LLC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>360</v>
+      </c>
+      <c r="F18" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>19</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="N18" t="n">
+        <v>59</v>
+      </c>
+      <c r="O18" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Overstocked (26 wks on hand) - confirm before buying more</t>
         </is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1375,9 +1372,6 @@
       <c r="O16" t="n">
         <v>55</v>
       </c>
-      <c r="P16" t="n">
-        <v>22</v>
-      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -1600,9 +1594,6 @@
       <c r="O20" t="n">
         <v>55</v>
       </c>
-      <c r="P20" t="n">
-        <v>22</v>
-      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -2403,11 +2394,7 @@
       <c r="O34" t="n">
         <v>48</v>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2821,14 +2808,7 @@
       <c r="O41" t="n">
         <v>54</v>
       </c>
-      <c r="P41" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -2885,9 +2865,6 @@
       </c>
       <c r="O42" t="n">
         <v>44</v>
-      </c>
-      <c r="P42" t="n">
-        <v>25.2</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -3125,11 +3102,7 @@
       <c r="O46" t="n">
         <v>48</v>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
     </row>
@@ -3307,9 +3280,6 @@
       <c r="O49" t="n">
         <v>60</v>
       </c>
-      <c r="P49" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -3550,9 +3520,6 @@
       <c r="O53" t="n">
         <v>44</v>
       </c>
-      <c r="P53" t="n">
-        <v>25.7</v>
-      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -3685,12 +3652,9 @@
       <c r="O55" t="n">
         <v>36</v>
       </c>
-      <c r="P55" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+          <t>ON AD - Sunday special (buy to 8w)</t>
         </is>
       </c>
       <c r="R55" t="inlineStr"/>
@@ -4733,9 +4697,6 @@
       <c r="O8" t="n">
         <v>60</v>
       </c>
-      <c r="P8" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4802,9 +4763,6 @@
       <c r="O9" t="n">
         <v>44</v>
       </c>
-      <c r="P9" t="n">
-        <v>25.7</v>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4937,12 +4895,9 @@
       <c r="O11" t="n">
         <v>36</v>
       </c>
-      <c r="P11" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+          <t>ON AD - Sunday special (buy to 8w)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1087,9 +1087,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1317,9 +1314,6 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
-      <c r="P15" t="n">
-        <v>22</v>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -1542,9 +1536,6 @@
       <c r="O19" t="n">
         <v>55</v>
       </c>
-      <c r="P19" t="n">
-        <v>22</v>
-      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -2523,11 +2514,7 @@
       <c r="O36" t="n">
         <v>48</v>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2585,14 +2572,7 @@
       <c r="O37" t="n">
         <v>54</v>
       </c>
-      <c r="P37" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
@@ -2766,14 +2746,7 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="P40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2889,9 +2862,6 @@
       <c r="O42" t="n">
         <v>44</v>
       </c>
-      <c r="P42" t="n">
-        <v>25.2</v>
-      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -3244,14 +3214,7 @@
       <c r="O48" t="n">
         <v>39</v>
       </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
@@ -3553,12 +3516,9 @@
       <c r="O53" t="n">
         <v>36</v>
       </c>
-      <c r="P53" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+          <t>ON AD - Sunday special (buy to 8w)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr"/>
@@ -3683,9 +3643,6 @@
       </c>
       <c r="O55" t="n">
         <v>44</v>
-      </c>
-      <c r="P55" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4484,14 +4441,7 @@
       <c r="O6" t="n">
         <v>39</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
@@ -4619,12 +4569,9 @@
       <c r="O8" t="n">
         <v>36</v>
       </c>
-      <c r="P8" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+          <t>ON AD - Sunday special (buy to 8w)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -4749,9 +4696,6 @@
       </c>
       <c r="O10" t="n">
         <v>44</v>
-      </c>
-      <c r="P10" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1087,9 +1087,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1317,9 +1314,6 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
-      <c r="P15" t="n">
-        <v>22</v>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -1600,9 +1594,6 @@
       <c r="O20" t="n">
         <v>55</v>
       </c>
-      <c r="P20" t="n">
-        <v>22</v>
-      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -2523,14 +2514,7 @@
       <c r="O36" t="n">
         <v>54</v>
       </c>
-      <c r="P36" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2646,14 +2630,7 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="P38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2827,9 +2804,6 @@
       <c r="O41" t="n">
         <v>43</v>
       </c>
-      <c r="P41" t="n">
-        <v>22</v>
-      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -3008,9 +2982,6 @@
       <c r="O44" t="n">
         <v>44</v>
       </c>
-      <c r="P44" t="n">
-        <v>25.2</v>
-      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -3069,14 +3040,7 @@
       <c r="O45" t="n">
         <v>54</v>
       </c>
-      <c r="P45" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3134,14 +3098,7 @@
       <c r="O46" t="n">
         <v>39</v>
       </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
@@ -3202,9 +3159,6 @@
       </c>
       <c r="O47" t="n">
         <v>45</v>
-      </c>
-      <c r="P47" t="n">
-        <v>17</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3264,9 +3218,6 @@
       <c r="O48" t="n">
         <v>60</v>
       </c>
-      <c r="P48" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -3573,12 +3524,9 @@
       <c r="O53" t="n">
         <v>36</v>
       </c>
-      <c r="P53" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+          <t>ON AD - Sunday special (buy to 8w)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr"/>
@@ -3703,9 +3651,6 @@
       </c>
       <c r="O55" t="n">
         <v>44</v>
-      </c>
-      <c r="P55" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4504,14 +4449,7 @@
       <c r="O6" t="n">
         <v>39</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
@@ -4573,9 +4511,6 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
-      <c r="P7" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4708,12 +4643,9 @@
       <c r="O9" t="n">
         <v>36</v>
       </c>
-      <c r="P9" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+          <t>ON AD - Sunday special (buy to 8w)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -4838,9 +4770,6 @@
       </c>
       <c r="O11" t="n">
         <v>44</v>
-      </c>
-      <c r="P11" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1087,9 +1087,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1428,9 +1425,6 @@
       <c r="O17" t="n">
         <v>55</v>
       </c>
-      <c r="P17" t="n">
-        <v>22</v>
-      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -1484,9 +1478,6 @@
       <c r="O18" t="n">
         <v>55</v>
       </c>
-      <c r="P18" t="n">
-        <v>22</v>
-      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -2635,14 +2626,7 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="P38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2700,14 +2684,7 @@
       <c r="O39" t="n">
         <v>54</v>
       </c>
-      <c r="P39" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
     </row>
@@ -2765,11 +2742,7 @@
       <c r="O40" t="n">
         <v>48</v>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2885,11 +2858,7 @@
       <c r="O42" t="n">
         <v>48</v>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
     </row>
@@ -2946,9 +2915,6 @@
       </c>
       <c r="O43" t="n">
         <v>45</v>
-      </c>
-      <c r="P43" t="n">
-        <v>17</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -3066,14 +3032,7 @@
       <c r="O45" t="n">
         <v>54</v>
       </c>
-      <c r="P45" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3130,9 +3089,6 @@
       </c>
       <c r="O46" t="n">
         <v>43</v>
-      </c>
-      <c r="P46" t="n">
-        <v>22</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3192,14 +3148,7 @@
       <c r="O47" t="n">
         <v>39</v>
       </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
@@ -3319,9 +3268,6 @@
       <c r="O49" t="n">
         <v>44</v>
       </c>
-      <c r="P49" t="n">
-        <v>25.2</v>
-      </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -3438,12 +3384,9 @@
       <c r="O51" t="n">
         <v>40</v>
       </c>
-      <c r="P51" t="n">
-        <v>18.3</v>
-      </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Buy a pallet, get 9cs of Gummies Free to hit invoice net of $47</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr"/>
@@ -3619,12 +3562,9 @@
       <c r="O54" t="n">
         <v>36</v>
       </c>
-      <c r="P54" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+          <t>ON AD - Sunday special (buy to 8w)</t>
         </is>
       </c>
       <c r="R54" t="inlineStr"/>
@@ -4059,9 +3999,6 @@
       </c>
       <c r="O61" t="n">
         <v>69</v>
-      </c>
-      <c r="P61" t="n">
-        <v>6.2</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4426,14 +4363,7 @@
       <c r="O4" t="n">
         <v>39</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -4495,12 +4425,9 @@
       <c r="O5" t="n">
         <v>36</v>
       </c>
-      <c r="P5" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+          <t>ON AD - Sunday special (buy to 8w)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -4935,9 +4862,6 @@
       </c>
       <c r="O12" t="n">
         <v>69</v>
-      </c>
-      <c r="P12" t="n">
-        <v>6.2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1087,9 +1087,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1201,9 +1198,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1315,9 +1309,6 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
-      <c r="P15" t="n">
-        <v>22</v>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -2221,9 +2212,6 @@
       <c r="O31" t="n">
         <v>48</v>
       </c>
-      <c r="P31" t="n">
-        <v>25.7</v>
-      </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
@@ -2642,14 +2630,7 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="P38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2707,14 +2688,7 @@
       <c r="O39" t="n">
         <v>39</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
@@ -2775,9 +2749,6 @@
       </c>
       <c r="O40" t="n">
         <v>43</v>
-      </c>
-      <c r="P40" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2895,11 +2866,7 @@
       <c r="O42" t="n">
         <v>48</v>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
     </row>
@@ -2957,11 +2924,7 @@
       <c r="O43" t="n">
         <v>73</v>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>60 Day Reorder Time</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3019,14 +2982,7 @@
       <c r="O44" t="n">
         <v>54</v>
       </c>
-      <c r="P44" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
@@ -3084,11 +3040,7 @@
       <c r="O45" t="n">
         <v>44</v>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3145,9 +3097,6 @@
       </c>
       <c r="O46" t="n">
         <v>60</v>
-      </c>
-      <c r="P46" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3323,14 +3272,7 @@
       <c r="O49" t="n">
         <v>54</v>
       </c>
-      <c r="P49" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
     </row>
@@ -3504,14 +3446,7 @@
       <c r="O52" t="n">
         <v>54</v>
       </c>
-      <c r="P52" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
     </row>
@@ -3627,9 +3562,6 @@
       <c r="O54" t="n">
         <v>60</v>
       </c>
-      <c r="P54" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
@@ -3750,9 +3682,6 @@
       <c r="O56" t="n">
         <v>44</v>
       </c>
-      <c r="P56" t="n">
-        <v>25.2</v>
-      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3869,11 +3798,7 @@
       <c r="O58" t="n">
         <v>73</v>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>60 Day Reorder Time</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
     </row>
@@ -3930,9 +3855,6 @@
       </c>
       <c r="O59" t="n">
         <v>60</v>
-      </c>
-      <c r="P59" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3996,9 +3918,6 @@
       <c r="O60" t="n">
         <v>45</v>
       </c>
-      <c r="P60" t="n">
-        <v>17</v>
-      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -4057,11 +3976,7 @@
       <c r="O61" t="n">
         <v>48</v>
       </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
     </row>
@@ -4177,14 +4092,7 @@
       <c r="O63" t="n">
         <v>45</v>
       </c>
-      <c r="P63" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
@@ -4253,12 +4161,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Gigli 10mg THC Variety Pack 12pk 12oz can</t>
+          <t>Gigli Extra Gigli Variety 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>199284006881</t>
+          <t>643459380004</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4272,58 +4180,51 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>451</v>
+        <v>330</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>73.8</v>
       </c>
       <c r="I65" t="n">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="J65" t="n">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="K65" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="L65" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>23.04</v>
+        <v>9.75</v>
       </c>
       <c r="N65" t="n">
-        <v>1382</v>
+        <v>58</v>
       </c>
       <c r="O65" t="n">
-        <v>47</v>
-      </c>
-      <c r="P65" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w); Buy a pallet, get 9cs of Gummies Free to hit invoice net of $47</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Gigli Extra Gigli Variety 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blueberry Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>643459380004</t>
+          <t>643459379992</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4337,34 +4238,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F66" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="G66" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H66" t="n">
-        <v>73.8</v>
+        <v>44.5</v>
       </c>
       <c r="I66" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="J66" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="K66" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
         <v>9.75</v>
       </c>
       <c r="N66" t="n">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="O66" t="n">
         <v>49</v>
@@ -4376,12 +4277,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Gigli Blueberry Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blood Orange Margarita 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>643459379992</t>
+          <t>643459380028</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4395,22 +4296,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="F67" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="G67" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="H67" t="n">
-        <v>44.5</v>
+        <v>35.5</v>
       </c>
       <c r="I67" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="J67" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K67" t="n">
         <v>12</v>
@@ -4434,12 +4335,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gigli Blood Orange Margarita 10mg THC 4pk 12oz can</t>
+          <t>Acre Ginger Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>643459380028</t>
+          <t>615867915949</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4449,55 +4350,63 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>56 Brewing</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>368</v>
+        <v>143</v>
       </c>
       <c r="F68" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H68" t="n">
-        <v>35.5</v>
+        <v>10.2</v>
       </c>
       <c r="I68" t="n">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="J68" t="n">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="K68" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>9.75</v>
+        <v>7.94</v>
       </c>
       <c r="N68" t="n">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="O68" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q68" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Overstocked (8 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Acre Ginger Lime 10mg THC 4pk 12oz can</t>
+          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>615867915949</t>
+          <t>643459379909</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4507,128 +4416,125 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>56 Brewing</t>
+          <t>Gigli MN LLC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>143</v>
+        <v>295</v>
       </c>
       <c r="F69" t="n">
-        <v>8.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="G69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>10.2</v>
+        <v>24.5</v>
       </c>
       <c r="I69" t="n">
+        <v>33</v>
+      </c>
+      <c r="J69" t="n">
+        <v>20</v>
+      </c>
+      <c r="K69" t="n">
         <v>12</v>
       </c>
-      <c r="J69" t="n">
-        <v>8</v>
-      </c>
-      <c r="K69" t="n">
-        <v>6</v>
-      </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>7.94</v>
+        <v>8.67</v>
       </c>
       <c r="N69" t="n">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="O69" t="n">
-        <v>36</v>
-      </c>
-      <c r="P69" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Overstocked (8 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
+          <t>Nothing But Hemp Maui Wowie 10mg THC 5 Pack</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>643459379909</t>
+          <t>649696422354</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Edibles</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>Nothing But Hemp LLC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>295</v>
+        <v>223</v>
       </c>
       <c r="F70" t="n">
-        <v>10.1</v>
+        <v>12.4</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H70" t="n">
-        <v>24.5</v>
+        <v>17.8</v>
       </c>
       <c r="I70" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
         <v>20</v>
       </c>
       <c r="K70" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>8.67</v>
+        <v>6.31</v>
       </c>
       <c r="N70" t="n">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="O70" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q70" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (12 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Bent Paddle Hightened Mary Jane's Mule 10mg THC 4pk 12oz can</t>
+          <t>IYKYK Lemonade 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>850024846630</t>
+          <t>850071300338</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4638,23 +4544,23 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Bent Paddle Brewing Co</t>
+          <t>IYKYK Beverages, LLC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>94</v>
+        <v>124.75</v>
       </c>
       <c r="F71" t="n">
-        <v>10.9</v>
+        <v>17.2</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H71" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4666,23 +4572,23 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>9.390000000000001</v>
+        <v>9</v>
       </c>
       <c r="N71" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O71" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - Sunday special (buy to 8w)</t>
         </is>
       </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (17 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
@@ -5069,7 +4975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5223,9 +5129,6 @@
       <c r="O2" t="n">
         <v>48</v>
       </c>
-      <c r="P2" t="n">
-        <v>25.7</v>
-      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
@@ -5412,14 +5315,7 @@
       <c r="O5" t="n">
         <v>39</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -5480,9 +5376,6 @@
       </c>
       <c r="O6" t="n">
         <v>60</v>
-      </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -5546,9 +5439,6 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
-      <c r="P7" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -5611,14 +5501,7 @@
       <c r="O8" t="n">
         <v>45</v>
       </c>
-      <c r="P8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
@@ -5680,12 +5563,9 @@
       <c r="O9" t="n">
         <v>36</v>
       </c>
-      <c r="P9" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 8w); 3cs Min Buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -5760,56 +5640,56 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bent Paddle Hightened Mary Jane's Mule 10mg THC 4pk 12oz can</t>
+          <t>Nothing But Hemp Maui Wowie 10mg THC 5 Pack</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>850024846630</t>
+          <t>649696422354</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Edibles</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bent Paddle Brewing Co</t>
+          <t>Nothing But Hemp LLC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>223</v>
       </c>
       <c r="F11" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>5.8</v>
+        <v>17.8</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>9.390000000000001</v>
+        <v>6.31</v>
       </c>
       <c r="N11" t="n">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="O11" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -5819,19 +5699,19 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (12 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gigli Raspberry Ginger Mule 10mg THC 4pk 12oz can</t>
+          <t>IYKYK Lemonade 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>643459379954</t>
+          <t>850071300338</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5841,59 +5721,63 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>IYKYK Beverages, LLC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>379</v>
+        <v>124.75</v>
       </c>
       <c r="F12" t="n">
-        <v>18.9</v>
+        <v>17.2</v>
       </c>
       <c r="G12" t="n">
-        <v>-6</v>
+        <v>35</v>
       </c>
       <c r="H12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>9.75</v>
+        <v>9</v>
       </c>
       <c r="N12" t="n">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="O12" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 8w)</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Overstocked (19 wks on hand) - confirm before buying more; Seasonal - last year ~36/wk vs 20 now, buy ahead?</t>
+          <t>Overstocked (17 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gigli Blood Orange Margarita 5mg THC 4pk 12oz can</t>
+          <t>Gigli Raspberry Ginger Mule 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>643459379916</t>
+          <t>643459379954</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5907,22 +5791,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>276</v>
+        <v>379</v>
       </c>
       <c r="F13" t="n">
-        <v>20.4</v>
+        <v>18.9</v>
       </c>
       <c r="G13" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>12</v>
@@ -5931,10 +5815,10 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>8.859999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="N13" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="O13" t="n">
         <v>49</v>
@@ -5943,19 +5827,19 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (19 wks on hand) - confirm before buying more; Seasonal - last year ~36/wk vs 20 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gigli Mango Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blood Orange Margarita 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>643459379541</t>
+          <t>643459379916</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5969,55 +5853,55 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>231</v>
+        <v>276</v>
       </c>
       <c r="F14" t="n">
-        <v>21.1</v>
+        <v>20.4</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>-5</v>
       </c>
       <c r="H14" t="n">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>9.779999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="O14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Overstocked (21 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Gigli Mango Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>198168611401</t>
+          <t>643459379541</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6031,34 +5915,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>176</v>
+        <v>231</v>
       </c>
       <c r="F15" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="G15" t="n">
-        <v>-10</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="I15" t="n">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="J15" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="O15" t="n">
         <v>48</v>
@@ -6067,19 +5951,19 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~15/wk vs 8 now, buy ahead?</t>
+          <t>Overstocked (21 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gigli Blueberry Lemonade 5mg THC 4pk 12oz can</t>
+          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>643459379947</t>
+          <t>198168611401</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6093,55 +5977,55 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>282</v>
+        <v>176</v>
       </c>
       <c r="F16" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="H16" t="n">
-        <v>7.5</v>
+        <v>15.2</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>8.73</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="O16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Overstocked (22 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~15/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gigli Citrus Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blueberry Lemonade 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>643459379305</t>
+          <t>643459379947</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6155,22 +6039,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>22.4</v>
       </c>
       <c r="G17" t="n">
-        <v>-37</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>19.8</v>
+        <v>7.5</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
@@ -6179,17 +6063,79 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>9.77</v>
+        <v>8.73</v>
       </c>
       <c r="N17" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="O17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
+        <is>
+          <t>Overstocked (22 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gigli Citrus Seltzer 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>643459379305</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Gigli MN LLC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>294</v>
+      </c>
+      <c r="F18" t="n">
+        <v>28</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-37</v>
+      </c>
+      <c r="H18" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>23</v>
+      </c>
+      <c r="J18" t="n">
+        <v>16</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="N18" t="n">
+        <v>59</v>
+      </c>
+      <c r="O18" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Overstocked (28 wks on hand) - confirm before buying more; Seasonal - last year ~20/wk vs 10 now, buy ahead?</t>
         </is>
@@ -6206,7 +6152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6299,75 +6245,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BLNCD Brain Boost Adaptogen 50mg THC Gummies 10pk</t>
+          <t>Brez Double 5mg THC 12oz can</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>810012698481</t>
+          <t>197644309047</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Edibles</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Nothing But Hemp LLC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-27</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>58.5</v>
       </c>
       <c r="I2" t="n">
+        <v>53</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>48</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
       <c r="M2" t="n">
-        <v>11.82</v>
+        <v>2.83</v>
       </c>
       <c r="N2" t="n">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="O2" t="n">
-        <v>41</v>
-      </c>
-      <c r="P2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brez Double 5mg THC 12oz can</t>
+          <t>Brez Single 2.5mg THC 7.5oz can</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>197644309047</t>
+          <t>197644087846</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6387,43 +6326,43 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>-16</v>
       </c>
       <c r="H3" t="n">
-        <v>58.5</v>
+        <v>51.8</v>
       </c>
       <c r="I3" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="N3" t="n">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="O3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brez Single 2.5mg THC 7.5oz can</t>
+          <t>Gigli Raspberry Tea 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>197644087846</t>
+          <t>198168016879</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6433,99 +6372,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nothing But Hemp LLC</t>
+          <t>Discontinued</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-16</v>
+        <v>-25</v>
       </c>
       <c r="H4" t="n">
-        <v>51.8</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>61</v>
+        <v>248</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>72</v>
+        <v>210</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>2.29</v>
+        <v>9.83</v>
       </c>
       <c r="N4" t="n">
-        <v>165</v>
+        <v>2065</v>
       </c>
       <c r="O4" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="Q4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Gigli Raspberry Tea 10mg THC 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>198168016879</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Discontinued</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>52</v>
-      </c>
-      <c r="F5" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H5" t="n">
-        <v>21</v>
-      </c>
-      <c r="I5" t="n">
-        <v>248</v>
-      </c>
-      <c r="J5" t="n">
-        <v>39</v>
-      </c>
-      <c r="K5" t="n">
-        <v>210</v>
-      </c>
-      <c r="L5" t="n">
-        <v>35</v>
-      </c>
-      <c r="M5" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2065</v>
-      </c>
-      <c r="O5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,6 +1029,9 @@
       <c r="O10" t="n">
         <v>55</v>
       </c>
+      <c r="P10" t="n">
+        <v>22</v>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1082,6 +1085,9 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
+      <c r="P11" t="n">
+        <v>22</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1193,6 +1199,9 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
+      <c r="P13" t="n">
+        <v>22</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -2506,7 +2515,14 @@
       <c r="O36" t="n">
         <v>39</v>
       </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
@@ -2567,6 +2583,9 @@
       </c>
       <c r="O37" t="n">
         <v>43</v>
+      </c>
+      <c r="P37" t="n">
+        <v>21.1</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2626,7 +2645,14 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="Q38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2742,6 +2768,9 @@
       <c r="O40" t="n">
         <v>60</v>
       </c>
+      <c r="P40" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -2800,7 +2829,14 @@
       <c r="O41" t="n">
         <v>54</v>
       </c>
-      <c r="Q41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -2916,7 +2952,14 @@
       <c r="O43" t="n">
         <v>54</v>
       </c>
-      <c r="Q43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -2973,6 +3016,9 @@
       </c>
       <c r="O44" t="n">
         <v>60</v>
+      </c>
+      <c r="P44" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -3090,7 +3136,14 @@
       <c r="O46" t="n">
         <v>54</v>
       </c>
-      <c r="Q46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
     </row>
@@ -3206,7 +3259,11 @@
       <c r="O48" t="n">
         <v>48</v>
       </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3322,7 +3379,11 @@
       <c r="O50" t="n">
         <v>44</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3380,7 +3441,14 @@
       <c r="O51" t="n">
         <v>45</v>
       </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
     </row>
@@ -3437,6 +3505,9 @@
       </c>
       <c r="O52" t="n">
         <v>60</v>
+      </c>
+      <c r="P52" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -3558,7 +3629,14 @@
       <c r="O54" t="n">
         <v>56</v>
       </c>
-      <c r="Q54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
     </row>
@@ -3616,7 +3694,11 @@
       <c r="O55" t="n">
         <v>48</v>
       </c>
-      <c r="Q55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3674,7 +3756,14 @@
       <c r="O56" t="n">
         <v>45</v>
       </c>
-      <c r="Q56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
@@ -3736,7 +3825,14 @@
       <c r="O57" t="n">
         <v>54</v>
       </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
     </row>
@@ -3793,6 +3889,9 @@
       </c>
       <c r="O58" t="n">
         <v>45</v>
+      </c>
+      <c r="P58" t="n">
+        <v>17</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -4084,6 +4183,9 @@
       <c r="O63" t="n">
         <v>43</v>
       </c>
+      <c r="P63" t="n">
+        <v>22</v>
+      </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
@@ -4378,9 +4480,12 @@
       <c r="O68" t="n">
         <v>36</v>
       </c>
+      <c r="P68" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
         </is>
       </c>
       <c r="R68" t="inlineStr"/>
@@ -4505,6 +4610,9 @@
       </c>
       <c r="O70" t="n">
         <v>64</v>
+      </c>
+      <c r="P70" t="n">
+        <v>70.8</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -5117,7 +5225,14 @@
       <c r="O3" t="n">
         <v>39</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -5178,6 +5293,9 @@
       </c>
       <c r="O4" t="n">
         <v>60</v>
+      </c>
+      <c r="P4" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -5241,7 +5359,14 @@
       <c r="O5" t="n">
         <v>45</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -5365,9 +5490,12 @@
       <c r="O7" t="n">
         <v>36</v>
       </c>
+      <c r="P7" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -5492,6 +5620,9 @@
       </c>
       <c r="O9" t="n">
         <v>64</v>
+      </c>
+      <c r="P9" t="n">
+        <v>70.8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -6032,6 +6163,9 @@
       <c r="O2" t="n">
         <v>44</v>
       </c>
+      <c r="P2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,9 +1029,6 @@
       <c r="O10" t="n">
         <v>55</v>
       </c>
-      <c r="P10" t="n">
-        <v>22</v>
-      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1085,9 +1082,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1199,9 +1193,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -2341,14 +2332,7 @@
       <c r="O33" t="n">
         <v>39</v>
       </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
@@ -2526,9 +2510,6 @@
       <c r="O36" t="n">
         <v>60</v>
       </c>
-      <c r="P36" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -2703,9 +2684,6 @@
       <c r="O39" t="n">
         <v>60</v>
       </c>
-      <c r="P39" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -2764,11 +2742,7 @@
       <c r="O40" t="n">
         <v>48</v>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2825,9 +2799,6 @@
       </c>
       <c r="O41" t="n">
         <v>43</v>
-      </c>
-      <c r="P41" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -2945,14 +2916,7 @@
       <c r="O43" t="n">
         <v>54</v>
       </c>
-      <c r="P43" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3126,14 +3090,7 @@
       <c r="O46" t="n">
         <v>54</v>
       </c>
-      <c r="P46" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
     </row>
@@ -3191,14 +3148,7 @@
       <c r="O47" t="n">
         <v>54</v>
       </c>
-      <c r="P47" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3314,14 +3264,7 @@
       <c r="O49" t="n">
         <v>45</v>
       </c>
-      <c r="P49" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
     </row>
@@ -3379,11 +3322,7 @@
       <c r="O50" t="n">
         <v>44</v>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3440,9 +3379,6 @@
       </c>
       <c r="O51" t="n">
         <v>60</v>
-      </c>
-      <c r="P51" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3564,14 +3500,7 @@
       <c r="O53" t="n">
         <v>54</v>
       </c>
-      <c r="P53" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
     </row>
@@ -3629,14 +3558,7 @@
       <c r="O54" t="n">
         <v>45</v>
       </c>
-      <c r="P54" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
@@ -3814,11 +3736,7 @@
       <c r="O57" t="n">
         <v>48</v>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
     </row>
@@ -3876,14 +3794,7 @@
       <c r="O58" t="n">
         <v>54</v>
       </c>
-      <c r="P58" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
     </row>
@@ -4289,12 +4200,9 @@
       <c r="O65" t="n">
         <v>42</v>
       </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Pallet Orders</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R65" t="inlineStr"/>
@@ -4358,12 +4266,9 @@
       <c r="O66" t="n">
         <v>36</v>
       </c>
-      <c r="P66" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R66" t="inlineStr"/>
@@ -4488,9 +4393,6 @@
       </c>
       <c r="O68" t="n">
         <v>65</v>
-      </c>
-      <c r="P68" t="n">
-        <v>70.8</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -5103,14 +5005,7 @@
       <c r="O3" t="n">
         <v>39</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -5171,9 +5066,6 @@
       </c>
       <c r="O4" t="n">
         <v>60</v>
-      </c>
-      <c r="P4" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -5237,14 +5129,7 @@
       <c r="O5" t="n">
         <v>45</v>
       </c>
-      <c r="P5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -5306,12 +5191,9 @@
       <c r="O6" t="n">
         <v>42</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Pallet Orders</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -5375,12 +5257,9 @@
       <c r="O7" t="n">
         <v>36</v>
       </c>
-      <c r="P7" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -5505,9 +5384,6 @@
       </c>
       <c r="O9" t="n">
         <v>65</v>
-      </c>
-      <c r="P9" t="n">
-        <v>70.8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -6048,9 +5924,6 @@
       <c r="O2" t="n">
         <v>44</v>
       </c>
-      <c r="P2" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,6 +971,9 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
+      <c r="P9" t="n">
+        <v>22</v>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1082,6 +1085,9 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
+      <c r="P11" t="n">
+        <v>22</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1193,6 +1199,9 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
+      <c r="P13" t="n">
+        <v>22</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -2101,7 +2110,14 @@
       <c r="O29" t="n">
         <v>39</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
@@ -2221,7 +2237,11 @@
       <c r="O31" t="n">
         <v>48</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
@@ -2453,7 +2473,14 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="Q35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2569,6 +2596,9 @@
       <c r="O37" t="n">
         <v>60</v>
       </c>
+      <c r="P37" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -2689,7 +2719,11 @@
       <c r="O39" t="n">
         <v>48</v>
       </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
     </row>
@@ -2863,7 +2897,14 @@
       <c r="O42" t="n">
         <v>54</v>
       </c>
-      <c r="Q42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
     </row>
@@ -2921,7 +2962,14 @@
       <c r="O43" t="n">
         <v>54</v>
       </c>
-      <c r="Q43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -2979,7 +3027,14 @@
       <c r="O44" t="n">
         <v>45</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
@@ -3095,6 +3150,9 @@
       <c r="O46" t="n">
         <v>60</v>
       </c>
+      <c r="P46" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3153,6 +3211,9 @@
       <c r="O47" t="n">
         <v>60</v>
       </c>
+      <c r="P47" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
@@ -3273,7 +3334,14 @@
       <c r="O49" t="n">
         <v>45</v>
       </c>
-      <c r="Q49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
@@ -3335,7 +3403,11 @@
       <c r="O50" t="n">
         <v>44</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3678,6 +3750,9 @@
       <c r="O56" t="n">
         <v>43</v>
       </c>
+      <c r="P56" t="n">
+        <v>22</v>
+      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3794,6 +3869,9 @@
       <c r="O58" t="n">
         <v>43</v>
       </c>
+      <c r="P58" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3914,6 +3992,9 @@
       <c r="O60" t="n">
         <v>45</v>
       </c>
+      <c r="P60" t="n">
+        <v>17</v>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -4030,7 +4111,14 @@
       <c r="O62" t="n">
         <v>56</v>
       </c>
-      <c r="Q62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
@@ -4146,7 +4234,14 @@
       <c r="O64" t="n">
         <v>54</v>
       </c>
-      <c r="Q64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
     </row>
@@ -4204,7 +4299,11 @@
       <c r="O65" t="n">
         <v>48</v>
       </c>
-      <c r="Q65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
@@ -4324,7 +4423,14 @@
       <c r="O67" t="n">
         <v>30</v>
       </c>
-      <c r="Q67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Case 1</t>
+        </is>
+      </c>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
@@ -4564,9 +4670,12 @@
       <c r="O71" t="n">
         <v>42</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); Pallet Orders</t>
         </is>
       </c>
       <c r="R71" t="inlineStr"/>
@@ -4692,9 +4801,12 @@
       <c r="O73" t="n">
         <v>39</v>
       </c>
+      <c r="P73" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
         </is>
       </c>
       <c r="R73" t="inlineStr"/>
@@ -5241,7 +5353,14 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5365,6 +5484,9 @@
       <c r="O4" t="n">
         <v>60</v>
       </c>
+      <c r="P4" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
@@ -5427,7 +5549,14 @@
       <c r="O5" t="n">
         <v>45</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -5551,7 +5680,11 @@
       <c r="O7" t="n">
         <v>48</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
@@ -5613,7 +5746,14 @@
       <c r="O8" t="n">
         <v>30</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Case 1</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
@@ -5737,9 +5877,12 @@
       <c r="O10" t="n">
         <v>42</v>
       </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); Pallet Orders</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -5865,9 +6008,12 @@
       <c r="O12" t="n">
         <v>39</v>
       </c>
+      <c r="P12" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -6260,7 +6406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6353,68 +6499,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brez Double 5mg THC 12oz can</t>
+          <t>BLNCD Brain Boost Adaptogen 50mg THC Gummies 10pk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>197644309047</t>
+          <t>810012698481</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Edibles</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nothing But Hemp LLC</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="G2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>51</v>
-      </c>
-      <c r="I2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>48</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
       <c r="M2" t="n">
-        <v>2.83</v>
+        <v>11.76</v>
       </c>
       <c r="N2" t="n">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="O2" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="P2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 8w)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brez Single 2.5mg THC 7.5oz can</t>
+          <t>Brez Double 5mg THC 12oz can</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>197644087846</t>
+          <t>197644309047</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6434,13 +6587,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-34</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>46.5</v>
+        <v>51</v>
       </c>
       <c r="I3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -6452,71 +6605,127 @@
         <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.29</v>
+        <v>2.83</v>
       </c>
       <c r="N3" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="O3" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Brez Single 2.5mg THC 7.5oz can</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>197644087846</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Nothing But Hemp LLC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>49</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>48</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N4" t="n">
+        <v>110</v>
+      </c>
+      <c r="O4" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Gigli Raspberry Tea 10mg THC 4pk 12oz can</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>198168016879</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Beverages</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>49</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>52.5</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>-71</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>18.2</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>250</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J5" t="n">
         <v>40</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K5" t="n">
         <v>210</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L5" t="n">
         <v>35</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M5" t="n">
         <v>9.84</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N5" t="n">
         <v>2066</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O5" t="n">
         <v>48</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,9 +971,6 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
-      <c r="P9" t="n">
-        <v>22</v>
-      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1085,9 +1082,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1199,9 +1193,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -2168,14 +2159,7 @@
       <c r="O30" t="n">
         <v>39</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
@@ -2295,11 +2279,7 @@
       <c r="O32" t="n">
         <v>48</v>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
@@ -2473,14 +2453,7 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="P35" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2537,9 +2510,6 @@
       </c>
       <c r="O36" t="n">
         <v>60</v>
-      </c>
-      <c r="P36" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2719,14 +2689,7 @@
       <c r="O39" t="n">
         <v>54</v>
       </c>
-      <c r="P39" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
     </row>
@@ -2784,11 +2747,7 @@
       <c r="O40" t="n">
         <v>48</v>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2846,14 +2805,7 @@
       <c r="O41" t="n">
         <v>54</v>
       </c>
-      <c r="P41" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -2910,9 +2862,6 @@
       </c>
       <c r="O42" t="n">
         <v>43</v>
-      </c>
-      <c r="P42" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2972,14 +2921,7 @@
       <c r="O43" t="n">
         <v>45</v>
       </c>
-      <c r="P43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3153,9 +3095,6 @@
       <c r="O46" t="n">
         <v>60</v>
       </c>
-      <c r="P46" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3214,14 +3153,7 @@
       <c r="O47" t="n">
         <v>45</v>
       </c>
-      <c r="P47" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
@@ -3341,9 +3273,6 @@
       <c r="O49" t="n">
         <v>60</v>
       </c>
-      <c r="P49" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -3642,11 +3571,7 @@
       <c r="O54" t="n">
         <v>44</v>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
     </row>
@@ -3877,14 +3802,7 @@
       <c r="O58" t="n">
         <v>56</v>
       </c>
-      <c r="P58" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
     </row>
@@ -4058,9 +3976,6 @@
       <c r="O61" t="n">
         <v>43</v>
       </c>
-      <c r="P61" t="n">
-        <v>22</v>
-      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
@@ -4119,14 +4034,7 @@
       <c r="O62" t="n">
         <v>54</v>
       </c>
-      <c r="P62" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
@@ -4183,9 +4091,6 @@
       </c>
       <c r="O63" t="n">
         <v>45</v>
-      </c>
-      <c r="P63" t="n">
-        <v>17</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -4361,14 +4266,7 @@
       <c r="O66" t="n">
         <v>30</v>
       </c>
-      <c r="P66" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
@@ -4492,11 +4390,7 @@
       <c r="O68" t="n">
         <v>48</v>
       </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
@@ -4558,9 +4452,6 @@
       <c r="O69" t="n">
         <v>44</v>
       </c>
-      <c r="P69" t="n">
-        <v>25.2</v>
-      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4623,9 +4514,6 @@
       <c r="O70" t="n">
         <v>31</v>
       </c>
-      <c r="P70" t="n">
-        <v>13.3</v>
-      </c>
       <c r="Q70" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4687,9 +4575,6 @@
       </c>
       <c r="O71" t="n">
         <v>37</v>
-      </c>
-      <c r="P71" t="n">
-        <v>20</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5542,14 +5427,7 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5673,14 +5551,7 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="P4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -5741,9 +5612,6 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -5873,14 +5741,7 @@
       <c r="O7" t="n">
         <v>30</v>
       </c>
-      <c r="P7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
@@ -6004,11 +5865,7 @@
       <c r="O9" t="n">
         <v>48</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,9 +971,6 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
-      <c r="P9" t="n">
-        <v>22</v>
-      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1085,9 +1082,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1199,9 +1193,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -2168,14 +2159,7 @@
       <c r="O30" t="n">
         <v>39</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
@@ -2411,11 +2395,7 @@
       <c r="O34" t="n">
         <v>48</v>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2473,14 +2453,7 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="P35" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2537,9 +2510,6 @@
       </c>
       <c r="O36" t="n">
         <v>60</v>
-      </c>
-      <c r="P36" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2657,11 +2627,7 @@
       <c r="O38" t="n">
         <v>48</v>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2719,14 +2685,7 @@
       <c r="O39" t="n">
         <v>54</v>
       </c>
-      <c r="P39" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
     </row>
@@ -2784,14 +2743,7 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="P40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2911,9 +2863,6 @@
       <c r="O42" t="n">
         <v>43</v>
       </c>
-      <c r="P42" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -2972,14 +2921,7 @@
       <c r="O43" t="n">
         <v>45</v>
       </c>
-      <c r="P43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3095,9 +3037,6 @@
       <c r="O45" t="n">
         <v>60</v>
       </c>
-      <c r="P45" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -3330,14 +3269,7 @@
       <c r="O49" t="n">
         <v>45</v>
       </c>
-      <c r="P49" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
@@ -3457,9 +3389,6 @@
       <c r="O51" t="n">
         <v>60</v>
       </c>
-      <c r="P51" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -3762,11 +3691,7 @@
       <c r="O56" t="n">
         <v>44</v>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
     </row>
@@ -3877,14 +3802,7 @@
       <c r="O58" t="n">
         <v>56</v>
       </c>
-      <c r="P58" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
     </row>
@@ -4000,14 +3918,7 @@
       <c r="O60" t="n">
         <v>54</v>
       </c>
-      <c r="P60" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
@@ -4064,9 +3975,6 @@
       </c>
       <c r="O61" t="n">
         <v>43</v>
-      </c>
-      <c r="P61" t="n">
-        <v>22</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -4424,14 +4332,7 @@
       <c r="O67" t="n">
         <v>30</v>
       </c>
-      <c r="P67" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
@@ -4493,14 +4394,7 @@
       <c r="O68" t="n">
         <v>54</v>
       </c>
-      <c r="P68" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4557,9 +4451,6 @@
       </c>
       <c r="O69" t="n">
         <v>45</v>
-      </c>
-      <c r="P69" t="n">
-        <v>17</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4677,9 +4568,6 @@
       <c r="O71" t="n">
         <v>44</v>
       </c>
-      <c r="P71" t="n">
-        <v>25.2</v>
-      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4742,9 +4630,6 @@
       <c r="O72" t="n">
         <v>37</v>
       </c>
-      <c r="P72" t="n">
-        <v>20</v>
-      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>ON AD - Sunday special (buy to 8w)</t>
@@ -4810,9 +4695,6 @@
       </c>
       <c r="O73" t="n">
         <v>31</v>
-      </c>
-      <c r="P73" t="n">
-        <v>13.3</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -5181,9 +5063,6 @@
       </c>
       <c r="O79" t="n">
         <v>45</v>
-      </c>
-      <c r="P79" t="n">
-        <v>30</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -5734,14 +5613,7 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5865,14 +5737,7 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="P4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -5933,9 +5798,6 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -6189,14 +6051,7 @@
       <c r="O9" t="n">
         <v>30</v>
       </c>
-      <c r="P9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6257,9 +6112,6 @@
       </c>
       <c r="O10" t="n">
         <v>37</v>
-      </c>
-      <c r="P10" t="n">
-        <v>20</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -6516,9 +6368,6 @@
       </c>
       <c r="O14" t="n">
         <v>45</v>
-      </c>
-      <c r="P14" t="n">
-        <v>30</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,6 +971,9 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
+      <c r="P9" t="n">
+        <v>22</v>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1024,6 +1027,9 @@
       <c r="O10" t="n">
         <v>55</v>
       </c>
+      <c r="P10" t="n">
+        <v>22</v>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1193,6 +1199,9 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
+      <c r="P13" t="n">
+        <v>22</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -2159,7 +2168,14 @@
       <c r="O30" t="n">
         <v>39</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
@@ -2279,6 +2295,9 @@
       <c r="O32" t="n">
         <v>60</v>
       </c>
+      <c r="P32" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -2337,7 +2356,11 @@
       <c r="O33" t="n">
         <v>48</v>
       </c>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
     </row>
@@ -2457,7 +2480,11 @@
       <c r="O35" t="n">
         <v>48</v>
       </c>
-      <c r="Q35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2515,7 +2542,14 @@
       <c r="O36" t="n">
         <v>54</v>
       </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2631,6 +2665,9 @@
       <c r="O38" t="n">
         <v>60</v>
       </c>
+      <c r="P38" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -2747,7 +2784,14 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="Q40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2863,6 +2907,9 @@
       <c r="O42" t="n">
         <v>43</v>
       </c>
+      <c r="P42" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -2979,6 +3026,9 @@
       <c r="O44" t="n">
         <v>60</v>
       </c>
+      <c r="P44" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
@@ -3041,7 +3091,14 @@
       <c r="O45" t="n">
         <v>45</v>
       </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
@@ -3277,7 +3334,14 @@
       <c r="O49" t="n">
         <v>54</v>
       </c>
-      <c r="Q49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
     </row>
@@ -3393,7 +3457,14 @@
       <c r="O51" t="n">
         <v>56</v>
       </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
     </row>
@@ -3566,6 +3637,9 @@
       <c r="O54" t="n">
         <v>43</v>
       </c>
+      <c r="P54" t="n">
+        <v>22</v>
+      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
@@ -3624,7 +3698,11 @@
       <c r="O55" t="n">
         <v>44</v>
       </c>
-      <c r="Q55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3740,7 +3818,14 @@
       <c r="O57" t="n">
         <v>45</v>
       </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
     </row>
@@ -4150,6 +4235,9 @@
       <c r="O64" t="n">
         <v>37</v>
       </c>
+      <c r="P64" t="n">
+        <v>20</v>
+      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>ON AD - Sunday special (buy to 8w)</t>
@@ -4215,6 +4303,9 @@
       </c>
       <c r="O65" t="n">
         <v>38</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4575,7 +4666,14 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -4699,6 +4797,9 @@
       <c r="O4" t="n">
         <v>60</v>
       </c>
+      <c r="P4" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
@@ -4761,7 +4862,14 @@
       <c r="O5" t="n">
         <v>45</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -4946,6 +5054,9 @@
       </c>
       <c r="O8" t="n">
         <v>37</v>
+      </c>
+      <c r="P8" t="n">
+        <v>20</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,9 +971,6 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
-      <c r="P9" t="n">
-        <v>22</v>
-      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1027,9 +1024,6 @@
       <c r="O10" t="n">
         <v>55</v>
       </c>
-      <c r="P10" t="n">
-        <v>22</v>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>ON AD - Sunday special (buy to 8w)</t>
@@ -1203,9 +1197,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -2172,14 +2163,7 @@
       <c r="O30" t="n">
         <v>39</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
@@ -2415,14 +2399,7 @@
       <c r="O34" t="n">
         <v>54</v>
       </c>
-      <c r="P34" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2707,14 +2684,7 @@
       <c r="O39" t="n">
         <v>54</v>
       </c>
-      <c r="P39" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
     </row>
@@ -2834,14 +2804,7 @@
       <c r="O41" t="n">
         <v>45</v>
       </c>
-      <c r="P41" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
@@ -2902,9 +2865,6 @@
       </c>
       <c r="O42" t="n">
         <v>60</v>
-      </c>
-      <c r="P42" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -3022,9 +2982,6 @@
       <c r="O44" t="n">
         <v>60</v>
       </c>
-      <c r="P44" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
@@ -3087,11 +3044,7 @@
       <c r="O45" t="n">
         <v>48</v>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3207,9 +3160,6 @@
       <c r="O47" t="n">
         <v>43</v>
       </c>
-      <c r="P47" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -3384,14 +3334,7 @@
       <c r="O50" t="n">
         <v>56</v>
       </c>
-      <c r="P50" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3507,9 +3450,6 @@
       <c r="O52" t="n">
         <v>60</v>
       </c>
-      <c r="P52" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
@@ -3568,11 +3508,7 @@
       <c r="O53" t="n">
         <v>48</v>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
     </row>
@@ -3692,14 +3628,7 @@
       <c r="O55" t="n">
         <v>54</v>
       </c>
-      <c r="P55" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3815,9 +3744,6 @@
       <c r="O57" t="n">
         <v>43</v>
       </c>
-      <c r="P57" t="n">
-        <v>22</v>
-      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -4166,11 +4092,7 @@
       <c r="O63" t="n">
         <v>47</v>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4228,11 +4150,7 @@
       <c r="O64" t="n">
         <v>44</v>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
-        </is>
-      </c>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
     </row>
@@ -4348,14 +4266,7 @@
       <c r="O66" t="n">
         <v>47</v>
       </c>
-      <c r="P66" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
     </row>
@@ -4529,14 +4440,7 @@
       <c r="O69" t="n">
         <v>45</v>
       </c>
-      <c r="P69" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
     </row>
@@ -4594,11 +4498,7 @@
       <c r="O70" t="n">
         <v>48</v>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
@@ -4722,9 +4622,6 @@
       <c r="O72" t="n">
         <v>45</v>
       </c>
-      <c r="P72" t="n">
-        <v>17</v>
-      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4787,12 +4684,9 @@
       <c r="O73" t="n">
         <v>42</v>
       </c>
-      <c r="P73" t="n">
-        <v>20</v>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R73" t="inlineStr"/>
@@ -5273,14 +5167,7 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5404,14 +5291,7 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="P4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -5472,9 +5352,6 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -5600,11 +5477,7 @@
       <c r="O7" t="n">
         <v>48</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
@@ -5728,12 +5601,9 @@
       <c r="O9" t="n">
         <v>42</v>
       </c>
-      <c r="P9" t="n">
-        <v>20</v>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,9 +971,6 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
-      <c r="P9" t="n">
-        <v>22</v>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>ON AD - Sunday special (buy to 8w)</t>
@@ -1030,9 +1027,6 @@
       </c>
       <c r="O10" t="n">
         <v>55</v>
-      </c>
-      <c r="P10" t="n">
-        <v>22</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1203,9 +1197,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -2056,14 +2047,7 @@
       <c r="O28" t="n">
         <v>39</v>
       </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
@@ -2299,14 +2283,7 @@
       <c r="O32" t="n">
         <v>54</v>
       </c>
-      <c r="P32" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
@@ -2422,14 +2399,7 @@
       <c r="O34" t="n">
         <v>54</v>
       </c>
-      <c r="P34" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2545,9 +2515,6 @@
       <c r="O36" t="n">
         <v>43</v>
       </c>
-      <c r="P36" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -2953,9 +2920,6 @@
       <c r="O43" t="n">
         <v>60</v>
       </c>
-      <c r="P43" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3014,14 +2978,7 @@
       <c r="O44" t="n">
         <v>45</v>
       </c>
-      <c r="P44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
@@ -3083,11 +3040,7 @@
       <c r="O45" t="n">
         <v>48</v>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3203,14 +3156,7 @@
       <c r="O47" t="n">
         <v>56</v>
       </c>
-      <c r="P47" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3326,9 +3272,6 @@
       <c r="O49" t="n">
         <v>60</v>
       </c>
-      <c r="P49" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
@@ -3627,14 +3570,7 @@
       <c r="O54" t="n">
         <v>54</v>
       </c>
-      <c r="P54" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
     </row>
@@ -3691,9 +3627,6 @@
       </c>
       <c r="O55" t="n">
         <v>60</v>
-      </c>
-      <c r="P55" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3869,9 +3802,6 @@
       <c r="O58" t="n">
         <v>43</v>
       </c>
-      <c r="P58" t="n">
-        <v>22</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3988,11 +3918,7 @@
       <c r="O60" t="n">
         <v>48</v>
       </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
@@ -4224,14 +4150,7 @@
       <c r="O64" t="n">
         <v>45</v>
       </c>
-      <c r="P64" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
     </row>
@@ -4347,9 +4266,6 @@
       <c r="O66" t="n">
         <v>45</v>
       </c>
-      <c r="P66" t="n">
-        <v>17</v>
-      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4474,14 +4390,7 @@
       <c r="O68" t="n">
         <v>47</v>
       </c>
-      <c r="P68" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4539,12 +4448,9 @@
       <c r="O69" t="n">
         <v>43</v>
       </c>
-      <c r="P69" t="n">
-        <v>20</v>
-      </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R69" t="inlineStr"/>
@@ -5025,14 +4931,7 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5156,14 +5055,7 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="P4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -5224,9 +5116,6 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -5414,12 +5303,9 @@
       <c r="O8" t="n">
         <v>43</v>
       </c>
-      <c r="P8" t="n">
-        <v>20</v>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,9 +1029,6 @@
       <c r="O10" t="n">
         <v>55</v>
       </c>
-      <c r="P10" t="n">
-        <v>22</v>
-      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1085,9 +1082,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1257,9 +1251,6 @@
       <c r="O14" t="n">
         <v>55</v>
       </c>
-      <c r="P14" t="n">
-        <v>22</v>
-      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -2221,14 +2212,7 @@
       <c r="O31" t="n">
         <v>39</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
@@ -2348,14 +2332,7 @@
       <c r="O33" t="n">
         <v>54</v>
       </c>
-      <c r="P33" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
     </row>
@@ -2698,14 +2675,7 @@
       <c r="O39" t="n">
         <v>45</v>
       </c>
-      <c r="P39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
@@ -2767,14 +2737,7 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="P40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2832,14 +2795,7 @@
       <c r="O41" t="n">
         <v>56</v>
       </c>
-      <c r="P41" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -3129,9 +3085,6 @@
       <c r="O46" t="n">
         <v>60</v>
       </c>
-      <c r="P46" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3359,14 +3312,7 @@
       <c r="O50" t="n">
         <v>54</v>
       </c>
-      <c r="P50" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3544,9 +3490,6 @@
       <c r="O53" t="n">
         <v>60</v>
       </c>
-      <c r="P53" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
@@ -3667,14 +3610,7 @@
       <c r="O55" t="n">
         <v>54</v>
       </c>
-      <c r="P55" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3732,11 +3668,7 @@
       <c r="O56" t="n">
         <v>44</v>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
     </row>
@@ -3852,9 +3784,6 @@
       <c r="O58" t="n">
         <v>43</v>
       </c>
-      <c r="P58" t="n">
-        <v>22</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3913,9 +3842,6 @@
       <c r="O59" t="n">
         <v>60</v>
       </c>
-      <c r="P59" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
@@ -3978,14 +3904,7 @@
       <c r="O60" t="n">
         <v>54</v>
       </c>
-      <c r="P60" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
@@ -4275,9 +4194,6 @@
       <c r="O65" t="n">
         <v>57</v>
       </c>
-      <c r="P65" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
@@ -4452,11 +4368,7 @@
       <c r="O68" t="n">
         <v>48</v>
       </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4513,9 +4425,6 @@
       </c>
       <c r="O69" t="n">
         <v>43</v>
-      </c>
-      <c r="P69" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4575,14 +4484,7 @@
       <c r="O70" t="n">
         <v>45</v>
       </c>
-      <c r="P70" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
     </row>
@@ -4639,9 +4541,6 @@
       </c>
       <c r="O71" t="n">
         <v>47</v>
-      </c>
-      <c r="P71" t="n">
-        <v>13.7</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4701,14 +4600,7 @@
       <c r="O72" t="n">
         <v>40</v>
       </c>
-      <c r="P72" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Buy a pallet, get 9cs of Gummies Free to hit invoice net of $47</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
     </row>
@@ -4765,9 +4657,6 @@
       </c>
       <c r="O73" t="n">
         <v>45</v>
-      </c>
-      <c r="P73" t="n">
-        <v>17</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -5063,9 +4952,6 @@
       <c r="O78" t="n">
         <v>37</v>
       </c>
-      <c r="P78" t="n">
-        <v>20</v>
-      </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
@@ -5124,9 +5010,6 @@
       <c r="O79" t="n">
         <v>60</v>
       </c>
-      <c r="P79" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
@@ -5185,14 +5068,7 @@
       <c r="O80" t="n">
         <v>54</v>
       </c>
-      <c r="P80" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
     </row>
@@ -5312,14 +5188,7 @@
       <c r="O82" t="n">
         <v>47</v>
       </c>
-      <c r="P82" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
     </row>
@@ -5377,14 +5246,7 @@
       <c r="O83" t="n">
         <v>54</v>
       </c>
-      <c r="P83" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
     </row>
@@ -5624,12 +5486,9 @@
       <c r="O87" t="n">
         <v>45</v>
       </c>
-      <c r="P87" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); $200 order qty per store</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
@@ -5693,12 +5552,9 @@
       <c r="O88" t="n">
         <v>43</v>
       </c>
-      <c r="P88" t="n">
-        <v>20</v>
-      </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R88" t="inlineStr"/>
@@ -5940,9 +5796,6 @@
       <c r="O92" t="n">
         <v>57</v>
       </c>
-      <c r="P92" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -6004,9 +5857,6 @@
       </c>
       <c r="O93" t="n">
         <v>37</v>
-      </c>
-      <c r="P93" t="n">
-        <v>20</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -6136,12 +5986,9 @@
       <c r="O95" t="n">
         <v>56</v>
       </c>
-      <c r="P95" t="n">
-        <v>20</v>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); FG From Supplier</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R95" t="inlineStr"/>
@@ -6626,14 +6473,7 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6695,14 +6535,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6888,9 +6721,6 @@
       <c r="O6" t="n">
         <v>60</v>
       </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -7201,12 +7031,9 @@
       <c r="O11" t="n">
         <v>45</v>
       </c>
-      <c r="P11" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); $200 order qty per store</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -7270,12 +7097,9 @@
       <c r="O12" t="n">
         <v>43</v>
       </c>
-      <c r="P12" t="n">
-        <v>20</v>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -7338,9 +7162,6 @@
       </c>
       <c r="O13" t="n">
         <v>37</v>
-      </c>
-      <c r="P13" t="n">
-        <v>20</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -7470,12 +7291,9 @@
       <c r="O15" t="n">
         <v>56</v>
       </c>
-      <c r="P15" t="n">
-        <v>20</v>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); FG From Supplier</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,9 +971,6 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
-      <c r="P9" t="n">
-        <v>22</v>
-      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1085,9 +1082,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1257,9 +1251,6 @@
       <c r="O14" t="n">
         <v>55</v>
       </c>
-      <c r="P14" t="n">
-        <v>22</v>
-      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -2221,14 +2212,7 @@
       <c r="O31" t="n">
         <v>39</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
@@ -2348,14 +2332,7 @@
       <c r="O33" t="n">
         <v>54</v>
       </c>
-      <c r="P33" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
     </row>
@@ -2698,14 +2675,7 @@
       <c r="O39" t="n">
         <v>45</v>
       </c>
-      <c r="P39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
@@ -2825,14 +2795,7 @@
       <c r="O41" t="n">
         <v>54</v>
       </c>
-      <c r="P41" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -2948,14 +2911,7 @@
       <c r="O43" t="n">
         <v>56</v>
       </c>
-      <c r="P43" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3012,9 +2968,6 @@
       </c>
       <c r="O44" t="n">
         <v>60</v>
-      </c>
-      <c r="P44" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -3301,14 +3254,7 @@
       <c r="O49" t="n">
         <v>54</v>
       </c>
-      <c r="P49" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
     </row>
@@ -3365,9 +3311,6 @@
       </c>
       <c r="O50" t="n">
         <v>43</v>
-      </c>
-      <c r="P50" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3725,9 +3668,6 @@
       <c r="O56" t="n">
         <v>60</v>
       </c>
-      <c r="P56" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3786,14 +3726,7 @@
       <c r="O57" t="n">
         <v>54</v>
       </c>
-      <c r="P57" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
     </row>
@@ -3850,9 +3783,6 @@
       </c>
       <c r="O58" t="n">
         <v>60</v>
-      </c>
-      <c r="P58" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -4032,9 +3962,6 @@
       <c r="O61" t="n">
         <v>43</v>
       </c>
-      <c r="P61" t="n">
-        <v>22</v>
-      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
@@ -4093,14 +4020,7 @@
       <c r="O62" t="n">
         <v>54</v>
       </c>
-      <c r="P62" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
@@ -4390,9 +4310,6 @@
       <c r="O67" t="n">
         <v>48</v>
       </c>
-      <c r="P67" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
@@ -4451,11 +4368,7 @@
       <c r="O68" t="n">
         <v>44</v>
       </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4513,14 +4426,7 @@
       <c r="O69" t="n">
         <v>47</v>
       </c>
-      <c r="P69" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
     </row>
@@ -4578,11 +4484,7 @@
       <c r="O70" t="n">
         <v>48</v>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
     </row>
@@ -4698,9 +4600,6 @@
       <c r="O72" t="n">
         <v>45</v>
       </c>
-      <c r="P72" t="n">
-        <v>17</v>
-      </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
@@ -4821,9 +4720,6 @@
       <c r="O74" t="n">
         <v>60</v>
       </c>
-      <c r="P74" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
@@ -4882,14 +4778,7 @@
       <c r="O75" t="n">
         <v>54</v>
       </c>
-      <c r="P75" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
     </row>
@@ -4947,14 +4836,7 @@
       <c r="O76" t="n">
         <v>54</v>
       </c>
-      <c r="P76" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5128,11 +5010,7 @@
       <c r="O79" t="n">
         <v>48</v>
       </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
     </row>
@@ -5252,14 +5130,7 @@
       <c r="O81" t="n">
         <v>45</v>
       </c>
-      <c r="P81" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
     </row>
@@ -5379,9 +5250,6 @@
       <c r="O83" t="n">
         <v>37</v>
       </c>
-      <c r="P83" t="n">
-        <v>20</v>
-      </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
@@ -5498,12 +5366,9 @@
       <c r="O85" t="n">
         <v>45</v>
       </c>
-      <c r="P85" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); $200 order qty per store</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R85" t="inlineStr"/>
@@ -5567,12 +5432,9 @@
       <c r="O86" t="n">
         <v>43</v>
       </c>
-      <c r="P86" t="n">
-        <v>20</v>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R86" t="inlineStr"/>
@@ -5752,9 +5614,6 @@
       <c r="O89" t="n">
         <v>37</v>
       </c>
-      <c r="P89" t="n">
-        <v>20</v>
-      </c>
       <c r="Q89" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -5821,12 +5680,9 @@
       <c r="O90" t="n">
         <v>56</v>
       </c>
-      <c r="P90" t="n">
-        <v>20</v>
-      </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); FG From Supplier</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R90" t="inlineStr"/>
@@ -6377,14 +6233,7 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6446,14 +6295,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6639,9 +6481,6 @@
       <c r="O6" t="n">
         <v>60</v>
       </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -6890,12 +6729,9 @@
       <c r="O10" t="n">
         <v>45</v>
       </c>
-      <c r="P10" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); $200 order qty per store</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -6959,12 +6795,9 @@
       <c r="O11" t="n">
         <v>43</v>
       </c>
-      <c r="P11" t="n">
-        <v>20</v>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -7028,9 +6861,6 @@
       <c r="O12" t="n">
         <v>37</v>
       </c>
-      <c r="P12" t="n">
-        <v>20</v>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -7097,12 +6927,9 @@
       <c r="O13" t="n">
         <v>56</v>
       </c>
-      <c r="P13" t="n">
-        <v>20</v>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); FG From Supplier</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,9 +971,6 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
-      <c r="P9" t="n">
-        <v>22</v>
-      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1085,9 +1082,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1373,9 +1367,6 @@
       <c r="O16" t="n">
         <v>55</v>
       </c>
-      <c r="P16" t="n">
-        <v>22</v>
-      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -2221,14 +2212,7 @@
       <c r="O31" t="n">
         <v>39</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
@@ -2290,14 +2274,7 @@
       <c r="O32" t="n">
         <v>54</v>
       </c>
-      <c r="P32" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
@@ -2640,14 +2617,7 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="P38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2763,14 +2733,7 @@
       <c r="O40" t="n">
         <v>45</v>
       </c>
-      <c r="P40" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
@@ -3006,14 +2969,7 @@
       <c r="O44" t="n">
         <v>56</v>
       </c>
-      <c r="P44" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
@@ -3129,9 +3085,6 @@
       <c r="O46" t="n">
         <v>60</v>
       </c>
-      <c r="P46" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3190,14 +3143,7 @@
       <c r="O47" t="n">
         <v>54</v>
       </c>
-      <c r="P47" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3366,9 +3312,6 @@
       <c r="O50" t="n">
         <v>43</v>
       </c>
-      <c r="P50" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
@@ -3725,9 +3668,6 @@
       <c r="O56" t="n">
         <v>43</v>
       </c>
-      <c r="P56" t="n">
-        <v>22</v>
-      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3786,11 +3726,7 @@
       <c r="O57" t="n">
         <v>48</v>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
     </row>
@@ -3906,9 +3842,6 @@
       <c r="O59" t="n">
         <v>60</v>
       </c>
-      <c r="P59" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -4083,9 +4016,6 @@
       <c r="O62" t="n">
         <v>60</v>
       </c>
-      <c r="P62" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
@@ -4148,14 +4078,7 @@
       <c r="O63" t="n">
         <v>54</v>
       </c>
-      <c r="P63" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4387,14 +4310,7 @@
       <c r="O67" t="n">
         <v>54</v>
       </c>
-      <c r="P67" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4452,14 +4368,7 @@
       <c r="O68" t="n">
         <v>54</v>
       </c>
-      <c r="P68" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4633,9 +4542,6 @@
       <c r="O71" t="n">
         <v>45</v>
       </c>
-      <c r="P71" t="n">
-        <v>17</v>
-      </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
@@ -4752,9 +4658,6 @@
       <c r="O73" t="n">
         <v>48</v>
       </c>
-      <c r="P73" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
@@ -4813,14 +4716,7 @@
       <c r="O74" t="n">
         <v>54</v>
       </c>
-      <c r="P74" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
     </row>
@@ -4878,11 +4774,7 @@
       <c r="O75" t="n">
         <v>48</v>
       </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
     </row>
@@ -5002,14 +4894,7 @@
       <c r="O77" t="n">
         <v>47</v>
       </c>
-      <c r="P77" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
     </row>
@@ -5066,9 +4951,6 @@
       </c>
       <c r="O78" t="n">
         <v>60</v>
-      </c>
-      <c r="P78" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -5132,14 +5014,7 @@
       <c r="O79" t="n">
         <v>45</v>
       </c>
-      <c r="P79" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
     </row>
@@ -5259,9 +5134,6 @@
       <c r="O81" t="n">
         <v>37</v>
       </c>
-      <c r="P81" t="n">
-        <v>20</v>
-      </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
@@ -5378,14 +5250,7 @@
       <c r="O83" t="n">
         <v>44</v>
       </c>
-      <c r="P83" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
     </row>
@@ -5443,14 +5308,7 @@
       <c r="O84" t="n">
         <v>46</v>
       </c>
-      <c r="P84" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
@@ -5574,12 +5432,9 @@
       <c r="O86" t="n">
         <v>45</v>
       </c>
-      <c r="P86" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); $200 order qty per store</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R86" t="inlineStr"/>
@@ -5643,12 +5498,9 @@
       <c r="O87" t="n">
         <v>43</v>
       </c>
-      <c r="P87" t="n">
-        <v>20</v>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
@@ -5828,9 +5680,6 @@
       <c r="O90" t="n">
         <v>37</v>
       </c>
-      <c r="P90" t="n">
-        <v>20</v>
-      </c>
       <c r="Q90" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -5893,12 +5742,9 @@
       <c r="O91" t="n">
         <v>56</v>
       </c>
-      <c r="P91" t="n">
-        <v>20</v>
-      </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); FG From Supplier</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R91" t="inlineStr"/>
@@ -6449,14 +6295,7 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6518,14 +6357,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6711,9 +6543,6 @@
       <c r="O6" t="n">
         <v>60</v>
       </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -6838,9 +6667,6 @@
       <c r="O8" t="n">
         <v>60</v>
       </c>
-      <c r="P8" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -6965,14 +6791,7 @@
       <c r="O10" t="n">
         <v>46</v>
       </c>
-      <c r="P10" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
@@ -7096,12 +6915,9 @@
       <c r="O12" t="n">
         <v>45</v>
       </c>
-      <c r="P12" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); $200 order qty per store</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -7165,12 +6981,9 @@
       <c r="O13" t="n">
         <v>43</v>
       </c>
-      <c r="P13" t="n">
-        <v>20</v>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -7234,12 +7047,9 @@
       <c r="O14" t="n">
         <v>56</v>
       </c>
-      <c r="P14" t="n">
-        <v>20</v>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); FG From Supplier</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,9 +1029,6 @@
       <c r="O10" t="n">
         <v>55</v>
       </c>
-      <c r="P10" t="n">
-        <v>22</v>
-      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1085,9 +1082,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1547,9 +1541,6 @@
       <c r="O19" t="n">
         <v>55</v>
       </c>
-      <c r="P19" t="n">
-        <v>22</v>
-      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -2274,14 +2265,7 @@
       <c r="O32" t="n">
         <v>39</v>
       </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
@@ -2401,14 +2385,7 @@
       <c r="O34" t="n">
         <v>54</v>
       </c>
-      <c r="P34" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2698,14 +2675,7 @@
       <c r="O39" t="n">
         <v>45</v>
       </c>
-      <c r="P39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
@@ -2825,14 +2795,7 @@
       <c r="O41" t="n">
         <v>56</v>
       </c>
-      <c r="P41" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -2948,14 +2911,7 @@
       <c r="O43" t="n">
         <v>54</v>
       </c>
-      <c r="P43" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3071,9 +3027,6 @@
       <c r="O45" t="n">
         <v>60</v>
       </c>
-      <c r="P45" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -3190,14 +3143,7 @@
       <c r="O47" t="n">
         <v>54</v>
       </c>
-      <c r="P47" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3606,9 +3552,6 @@
       <c r="O54" t="n">
         <v>60</v>
       </c>
-      <c r="P54" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
@@ -3667,14 +3610,7 @@
       <c r="O55" t="n">
         <v>54</v>
       </c>
-      <c r="P55" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3732,11 +3668,7 @@
       <c r="O56" t="n">
         <v>48</v>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
     </row>
@@ -3793,9 +3725,6 @@
       </c>
       <c r="O57" t="n">
         <v>43</v>
-      </c>
-      <c r="P57" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3855,9 +3784,6 @@
       <c r="O58" t="n">
         <v>60</v>
       </c>
-      <c r="P58" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
@@ -3920,9 +3846,6 @@
       <c r="O59" t="n">
         <v>43</v>
       </c>
-      <c r="P59" t="n">
-        <v>22</v>
-      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -4155,11 +4078,7 @@
       <c r="O63" t="n">
         <v>48</v>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4391,14 +4310,7 @@
       <c r="O67" t="n">
         <v>54</v>
       </c>
-      <c r="P67" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4572,9 +4484,6 @@
       <c r="O70" t="n">
         <v>48</v>
       </c>
-      <c r="P70" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
@@ -4633,9 +4542,6 @@
       <c r="O71" t="n">
         <v>60</v>
       </c>
-      <c r="P71" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
@@ -4880,9 +4786,6 @@
       <c r="O75" t="n">
         <v>37</v>
       </c>
-      <c r="P75" t="n">
-        <v>20</v>
-      </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
@@ -4941,9 +4844,6 @@
       <c r="O76" t="n">
         <v>45</v>
       </c>
-      <c r="P76" t="n">
-        <v>17</v>
-      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
@@ -5184,14 +5084,7 @@
       <c r="O80" t="n">
         <v>54</v>
       </c>
-      <c r="P80" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
     </row>
@@ -5249,14 +5142,7 @@
       <c r="O81" t="n">
         <v>45</v>
       </c>
-      <c r="P81" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
     </row>
@@ -6033,14 +5919,7 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6102,14 +5981,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6295,9 +6167,6 @@
       <c r="O6" t="n">
         <v>60</v>
       </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -6359,9 +6228,6 @@
       </c>
       <c r="O7" t="n">
         <v>60</v>
-      </c>
-      <c r="P7" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
